--- a/data/MARKET_DATA.xlsx
+++ b/data/MARKET_DATA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEF983E-B606-4780-A31B-29AD005BC3F6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AC4467-DC79-4728-B11F-C3D83956984D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15120" windowHeight="11265" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cross_asset" sheetId="1" r:id="rId1"/>
@@ -277,9 +277,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
-  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -311,7 +308,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -339,22 +336,20 @@
       <tp t="s">
         <v>#N/A N/A</v>
         <stp/>
-        <stp>BQL|16442668336719213286</stp>
-        <tr r="A2" s="1"/>
+        <stp>BQL|1859270753969333931</stp>
+        <tr r="A2" s="2"/>
+      </tp>
+      <tp t="s">
+        <v>#N/A Requesting Data...3712679885</v>
+        <stp/>
+        <stp>BQL|4376642064956882349</stp>
+        <tr r="A1" s="3"/>
       </tp>
       <tp t="s">
         <v>#N/A N/A</v>
         <stp/>
-        <stp>BQL|12518993884661200114</stp>
-        <tr r="A2" s="2"/>
-      </tp>
-    </main>
-    <main first="bofaddin.rtdserver">
-      <tp t="s">
-        <v>#N/A N/A</v>
-        <stp/>
-        <stp>BQL|4376642064956882349</stp>
-        <tr r="A1" s="3"/>
+        <stp>BQL|821047468459768629</stp>
+        <tr r="A2" s="1"/>
       </tp>
     </main>
   </volType>
@@ -665,7 +660,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <f>_xll.BQL($B$1:$D$1, "dropna(px_last(dates=range(2023-01-02, 2026-05-11)))", "showids", "false", "showheaders", "false", "showallcols", "false")</f>
+        <f>_xll.BQL($B$1:$D$1, "dropna(px_last(dates=range(2023-01-02, 2026-05-18), per=D))", "showids", "false", "showheaders", "false", "showallcols", "false","cols=4;rows=881")</f>
         <v>44928</v>
       </c>
       <c r="B2" t="e">
@@ -12918,4915 +12913,1120 @@
       <c r="A877" s="1">
         <v>46153</v>
       </c>
-      <c r="B877" t="e">
-        <v>#N/A</v>
+      <c r="B877">
+        <v>7412.84</v>
       </c>
       <c r="C877">
-        <v>97.998001098632813</v>
+        <v>97.954999999999998</v>
       </c>
       <c r="D877">
-        <v>4.3892402648925781</v>
+        <v>4.4134435649999997</v>
       </c>
     </row>
     <row r="878" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A878" s="1">
-        <v>45804</v>
+        <v>46154</v>
       </c>
       <c r="B878">
-        <v>5921.54</v>
+        <v>7400.96</v>
       </c>
       <c r="C878">
-        <v>99.521000000000001</v>
+        <v>98.298000000000002</v>
       </c>
       <c r="D878">
-        <v>4.4436321259999998</v>
+        <v>4.4629840850000004</v>
       </c>
     </row>
     <row r="879" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A879" s="1">
-        <v>45805</v>
+        <v>46155</v>
       </c>
       <c r="B879">
-        <v>5888.55</v>
+        <v>7444.25</v>
       </c>
       <c r="C879">
-        <v>99.875010000000003</v>
+        <v>98.524000000000001</v>
       </c>
       <c r="D879">
-        <v>4.477313519</v>
+        <v>4.4688234329999998</v>
       </c>
     </row>
     <row r="880" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A880" s="1">
-        <v>45806</v>
+        <v>46156</v>
       </c>
       <c r="B880">
-        <v>5912.17</v>
+        <v>7501.24</v>
       </c>
       <c r="C880">
-        <v>99.278009999999995</v>
+        <v>98.819010000000006</v>
       </c>
       <c r="D880">
-        <v>4.4180226329999996</v>
+        <v>4.4815940860000003</v>
       </c>
     </row>
     <row r="881" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A881" s="1">
-        <v>45807</v>
+        <v>46157</v>
       </c>
       <c r="B881">
-        <v>5911.69</v>
+        <v>7408.5</v>
       </c>
       <c r="C881">
-        <v>99.328999999999994</v>
+        <v>99.284000000000006</v>
       </c>
       <c r="D881">
-        <v>4.4003500940000002</v>
+        <v>4.5933504100000002</v>
       </c>
     </row>
     <row r="882" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A882" s="1">
-        <v>45808</v>
-      </c>
-      <c r="B882">
-        <v>5911.69</v>
+        <v>46160</v>
+      </c>
+      <c r="B882" t="e">
+        <v>#N/A</v>
       </c>
       <c r="C882">
-        <v>99.328999999999994</v>
+        <v>99.359001159667969</v>
       </c>
       <c r="D882">
-        <v>4.4003500940000002</v>
+        <v>4.6272048950195313</v>
       </c>
     </row>
     <row r="883" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A883" s="1">
-        <v>45809</v>
-      </c>
-      <c r="B883">
-        <v>5911.69</v>
-      </c>
-      <c r="C883">
-        <v>99.328999999999994</v>
-      </c>
-      <c r="D883">
-        <v>4.4003500940000002</v>
-      </c>
+      <c r="A883" s="1"/>
     </row>
     <row r="884" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A884" s="1">
-        <v>45810</v>
-      </c>
-      <c r="B884">
-        <v>5935.94</v>
-      </c>
-      <c r="C884">
-        <v>98.706000000000003</v>
-      </c>
-      <c r="D884">
-        <v>4.4398512840000004</v>
-      </c>
+      <c r="A884" s="1"/>
     </row>
     <row r="885" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A885" s="1">
-        <v>45811</v>
-      </c>
-      <c r="B885">
-        <v>5970.37</v>
-      </c>
-      <c r="C885">
-        <v>99.227010000000007</v>
-      </c>
-      <c r="D885">
-        <v>4.4537372590000004</v>
-      </c>
+      <c r="A885" s="1"/>
     </row>
     <row r="886" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A886" s="1">
-        <v>45812</v>
-      </c>
-      <c r="B886">
-        <v>5970.81</v>
-      </c>
-      <c r="C886">
-        <v>98.787000000000006</v>
-      </c>
-      <c r="D886">
-        <v>4.3551726339999997</v>
-      </c>
+      <c r="A886" s="1"/>
     </row>
     <row r="887" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A887" s="1">
-        <v>45813</v>
-      </c>
-      <c r="B887">
-        <v>5939.3</v>
-      </c>
-      <c r="C887">
-        <v>98.741</v>
-      </c>
-      <c r="D887">
-        <v>4.3905797</v>
-      </c>
+      <c r="A887" s="1"/>
     </row>
     <row r="888" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A888" s="1">
-        <v>45814</v>
-      </c>
-      <c r="B888">
-        <v>6000.36</v>
-      </c>
-      <c r="C888">
-        <v>99.19</v>
-      </c>
-      <c r="D888">
-        <v>4.5055842400000001</v>
-      </c>
+      <c r="A888" s="1"/>
     </row>
     <row r="889" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A889" s="1">
-        <v>45815</v>
-      </c>
-      <c r="B889">
-        <v>6000.36</v>
-      </c>
-      <c r="C889">
-        <v>99.19</v>
-      </c>
-      <c r="D889">
-        <v>4.5055842400000001</v>
-      </c>
+      <c r="A889" s="1"/>
     </row>
     <row r="890" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A890" s="1">
-        <v>45816</v>
-      </c>
-      <c r="B890">
-        <v>6000.36</v>
-      </c>
-      <c r="C890">
-        <v>99.19</v>
-      </c>
-      <c r="D890">
-        <v>4.5055842400000001</v>
-      </c>
+      <c r="A890" s="1"/>
     </row>
     <row r="891" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A891" s="1">
-        <v>45817</v>
-      </c>
-      <c r="B891">
-        <v>6005.88</v>
-      </c>
-      <c r="C891">
-        <v>98.938999999999993</v>
-      </c>
-      <c r="D891">
-        <v>4.4737863539999996</v>
-      </c>
+      <c r="A891" s="1"/>
     </row>
     <row r="892" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A892" s="1">
-        <v>45818</v>
-      </c>
-      <c r="B892">
-        <v>6038.81</v>
-      </c>
-      <c r="C892">
-        <v>99.098010000000002</v>
-      </c>
-      <c r="D892">
-        <v>4.4698495859999996</v>
-      </c>
+      <c r="A892" s="1"/>
     </row>
     <row r="893" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A893" s="1">
-        <v>45819</v>
-      </c>
-      <c r="B893">
-        <v>6022.24</v>
-      </c>
-      <c r="C893">
-        <v>98.631</v>
-      </c>
-      <c r="D893">
-        <v>4.420322895</v>
-      </c>
+      <c r="A893" s="1"/>
     </row>
     <row r="894" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A894" s="1">
-        <v>45820</v>
-      </c>
-      <c r="B894">
-        <v>6045.26</v>
-      </c>
-      <c r="C894">
-        <v>97.921009999999995</v>
-      </c>
-      <c r="D894">
-        <v>4.3592000009999996</v>
-      </c>
+      <c r="A894" s="1"/>
     </row>
     <row r="895" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A895" s="1">
-        <v>45821</v>
-      </c>
-      <c r="B895">
-        <v>5976.97</v>
-      </c>
-      <c r="C895">
-        <v>98.184010000000001</v>
-      </c>
-      <c r="D895">
-        <v>4.3986768720000002</v>
-      </c>
+      <c r="A895" s="1"/>
     </row>
     <row r="896" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A896" s="1">
-        <v>45822</v>
-      </c>
-      <c r="B896">
-        <v>5976.97</v>
-      </c>
-      <c r="C896">
-        <v>98.184010000000001</v>
-      </c>
-      <c r="D896">
-        <v>4.3986768720000002</v>
-      </c>
-    </row>
-    <row r="897" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A897" s="1">
-        <v>45823</v>
-      </c>
-      <c r="B897">
-        <v>5976.97</v>
-      </c>
-      <c r="C897">
-        <v>98.184010000000001</v>
-      </c>
-      <c r="D897">
-        <v>4.3986768720000002</v>
-      </c>
-    </row>
-    <row r="898" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A898" s="1">
-        <v>45824</v>
-      </c>
-      <c r="B898">
-        <v>6033.11</v>
-      </c>
-      <c r="C898">
-        <v>97.998000000000005</v>
-      </c>
-      <c r="D898">
-        <v>4.4462294580000004</v>
-      </c>
-    </row>
-    <row r="899" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A899" s="1">
-        <v>45825</v>
-      </c>
-      <c r="B899">
-        <v>5982.72</v>
-      </c>
-      <c r="C899">
-        <v>98.820009999999996</v>
-      </c>
-      <c r="D899">
-        <v>4.3888449669999998</v>
-      </c>
-    </row>
-    <row r="900" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A900" s="1">
-        <v>45826</v>
-      </c>
-      <c r="B900">
-        <v>5980.87</v>
-      </c>
-      <c r="C900">
-        <v>98.905010000000004</v>
-      </c>
-      <c r="D900">
-        <v>4.3908624649999997</v>
-      </c>
-    </row>
-    <row r="901" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A901" s="1">
-        <v>45827</v>
-      </c>
-      <c r="B901">
-        <v>5980.87</v>
-      </c>
-      <c r="C901">
-        <v>98.905010000000004</v>
-      </c>
-      <c r="D901">
-        <v>4.3908624649999997</v>
-      </c>
-    </row>
-    <row r="902" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A902" s="1">
-        <v>45828</v>
-      </c>
-      <c r="B902">
-        <v>5967.84</v>
-      </c>
-      <c r="C902">
-        <v>98.707009999999997</v>
-      </c>
-      <c r="D902">
-        <v>4.375123501</v>
-      </c>
-    </row>
-    <row r="903" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A903" s="1">
-        <v>45829</v>
-      </c>
-      <c r="B903">
-        <v>5967.84</v>
-      </c>
-      <c r="C903">
-        <v>98.707009999999997</v>
-      </c>
-      <c r="D903">
-        <v>4.375123501</v>
-      </c>
-    </row>
-    <row r="904" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A904" s="1">
-        <v>45830</v>
-      </c>
-      <c r="B904">
-        <v>5967.84</v>
-      </c>
-      <c r="C904">
-        <v>98.707009999999997</v>
-      </c>
-      <c r="D904">
-        <v>4.375123501</v>
-      </c>
-    </row>
-    <row r="905" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A905" s="1">
-        <v>45831</v>
-      </c>
-      <c r="B905">
-        <v>6025.17</v>
-      </c>
-      <c r="C905">
-        <v>98.41601</v>
-      </c>
-      <c r="D905">
-        <v>4.3475351330000001</v>
-      </c>
-    </row>
-    <row r="906" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A906" s="1">
-        <v>45832</v>
-      </c>
-      <c r="B906">
-        <v>6092.18</v>
-      </c>
-      <c r="C906">
-        <v>97.858000000000004</v>
-      </c>
-      <c r="D906">
-        <v>4.2944984440000002</v>
-      </c>
-    </row>
-    <row r="907" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A907" s="1">
-        <v>45833</v>
-      </c>
-      <c r="B907">
-        <v>6092.16</v>
-      </c>
-      <c r="C907">
-        <v>97.679000000000002</v>
-      </c>
-      <c r="D907">
-        <v>4.2905797960000003</v>
-      </c>
-    </row>
-    <row r="908" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A908" s="1">
-        <v>45834</v>
-      </c>
-      <c r="B908">
-        <v>6141.02</v>
-      </c>
-      <c r="C908">
-        <v>97.147000000000006</v>
-      </c>
-      <c r="D908">
-        <v>4.2416944499999998</v>
-      </c>
-    </row>
-    <row r="909" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A909" s="1">
-        <v>45835</v>
-      </c>
-      <c r="B909">
-        <v>6173.07</v>
-      </c>
-      <c r="C909">
-        <v>97.400999999999996</v>
-      </c>
-      <c r="D909">
-        <v>4.2768635750000001</v>
-      </c>
-    </row>
-    <row r="910" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A910" s="1">
-        <v>45836</v>
-      </c>
-      <c r="B910">
-        <v>6173.07</v>
-      </c>
-      <c r="C910">
-        <v>97.400999999999996</v>
-      </c>
-      <c r="D910">
-        <v>4.2768635750000001</v>
-      </c>
-    </row>
-    <row r="911" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A911" s="1">
-        <v>45837</v>
-      </c>
-      <c r="B911">
-        <v>6173.07</v>
-      </c>
-      <c r="C911">
-        <v>97.400999999999996</v>
-      </c>
-      <c r="D911">
-        <v>4.2768635750000001</v>
-      </c>
-    </row>
-    <row r="912" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A912" s="1">
-        <v>45838</v>
-      </c>
-      <c r="B912">
-        <v>6204.95</v>
-      </c>
-      <c r="C912">
-        <v>96.875010000000003</v>
-      </c>
-      <c r="D912">
-        <v>4.227996826</v>
-      </c>
-    </row>
-    <row r="913" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A913" s="1">
-        <v>45839</v>
-      </c>
-      <c r="B913">
-        <v>6198.01</v>
-      </c>
-      <c r="C913">
-        <v>96.819010000000006</v>
-      </c>
-      <c r="D913">
-        <v>4.2416467669999998</v>
-      </c>
-    </row>
-    <row r="914" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A914" s="1">
-        <v>45840</v>
-      </c>
-      <c r="B914">
-        <v>6227.42</v>
-      </c>
-      <c r="C914">
-        <v>96.775999999999996</v>
-      </c>
-      <c r="D914">
-        <v>4.2768592830000003</v>
-      </c>
-    </row>
-    <row r="915" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A915" s="1">
-        <v>45841</v>
-      </c>
-      <c r="B915">
-        <v>6279.35</v>
-      </c>
-      <c r="C915">
-        <v>97.180009999999996</v>
-      </c>
-      <c r="D915">
-        <v>4.3457412719999997</v>
-      </c>
-    </row>
-    <row r="916" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A916" s="1">
-        <v>45842</v>
-      </c>
-      <c r="B916">
-        <v>6279.35</v>
-      </c>
-      <c r="C916">
-        <v>97.180009999999996</v>
-      </c>
-      <c r="D916">
-        <v>4.3457412719999997</v>
-      </c>
-    </row>
-    <row r="917" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A917" s="1">
-        <v>45843</v>
-      </c>
-      <c r="B917">
-        <v>6279.35</v>
-      </c>
-      <c r="C917">
-        <v>97.180009999999996</v>
-      </c>
-      <c r="D917">
-        <v>4.3457412719999997</v>
-      </c>
-    </row>
-    <row r="918" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A918" s="1">
-        <v>45844</v>
-      </c>
-      <c r="B918">
-        <v>6279.35</v>
-      </c>
-      <c r="C918">
-        <v>97.180009999999996</v>
-      </c>
-      <c r="D918">
-        <v>4.3457412719999997</v>
-      </c>
-    </row>
-    <row r="919" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A919" s="1">
-        <v>45845</v>
-      </c>
-      <c r="B919">
-        <v>6229.98</v>
-      </c>
-      <c r="C919">
-        <v>97.48</v>
-      </c>
-      <c r="D919">
-        <v>4.3793849949999997</v>
-      </c>
-    </row>
-    <row r="920" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A920" s="1">
-        <v>45846</v>
-      </c>
-      <c r="B920">
-        <v>6225.52</v>
-      </c>
-      <c r="C920">
-        <v>97.516009999999994</v>
-      </c>
-      <c r="D920">
-        <v>4.3992433550000003</v>
-      </c>
-    </row>
-    <row r="921" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A921" s="1">
-        <v>45847</v>
-      </c>
-      <c r="B921">
-        <v>6263.26</v>
-      </c>
-      <c r="C921">
-        <v>97.555009999999996</v>
-      </c>
-      <c r="D921">
-        <v>4.3319635390000002</v>
-      </c>
-    </row>
-    <row r="922" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A922" s="1">
-        <v>45848</v>
-      </c>
-      <c r="B922">
-        <v>6280.46</v>
-      </c>
-      <c r="C922">
-        <v>97.652010000000004</v>
-      </c>
-      <c r="D922">
-        <v>4.3497543329999999</v>
-      </c>
-    </row>
-    <row r="923" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A923" s="1">
-        <v>45849</v>
-      </c>
-      <c r="B923">
-        <v>6259.75</v>
-      </c>
-      <c r="C923">
-        <v>97.852999999999994</v>
-      </c>
-      <c r="D923">
-        <v>4.4093222619999999</v>
-      </c>
-    </row>
-    <row r="924" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A924" s="1">
-        <v>45850</v>
-      </c>
-      <c r="B924">
-        <v>6259.75</v>
-      </c>
-      <c r="C924">
-        <v>97.852999999999994</v>
-      </c>
-      <c r="D924">
-        <v>4.4093222619999999</v>
-      </c>
-    </row>
-    <row r="925" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A925" s="1">
-        <v>45851</v>
-      </c>
-      <c r="B925">
-        <v>6259.75</v>
-      </c>
-      <c r="C925">
-        <v>97.852999999999994</v>
-      </c>
-      <c r="D925">
-        <v>4.4093222619999999</v>
-      </c>
-    </row>
-    <row r="926" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A926" s="1">
-        <v>45852</v>
-      </c>
-      <c r="B926">
-        <v>6268.56</v>
-      </c>
-      <c r="C926">
-        <v>98.081000000000003</v>
-      </c>
-      <c r="D926">
-        <v>4.4332590100000004</v>
-      </c>
-    </row>
-    <row r="927" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A927" s="1">
-        <v>45853</v>
-      </c>
-      <c r="B927">
-        <v>6243.76</v>
-      </c>
-      <c r="C927">
-        <v>98.616</v>
-      </c>
-      <c r="D927">
-        <v>4.4812812810000002</v>
-      </c>
-    </row>
-    <row r="928" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A928" s="1">
-        <v>45854</v>
-      </c>
-      <c r="B928">
-        <v>6263.7</v>
-      </c>
-      <c r="C928">
-        <v>98.392009999999999</v>
-      </c>
-      <c r="D928">
-        <v>4.4553017620000004</v>
-      </c>
-    </row>
-    <row r="929" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A929" s="1">
-        <v>45855</v>
-      </c>
-      <c r="B929">
-        <v>6297.36</v>
-      </c>
-      <c r="C929">
-        <v>98.733999999999995</v>
-      </c>
-      <c r="D929">
-        <v>4.4513435360000004</v>
-      </c>
-    </row>
-    <row r="930" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A930" s="1">
-        <v>45856</v>
-      </c>
-      <c r="B930">
-        <v>6296.79</v>
-      </c>
-      <c r="C930">
-        <v>98.481999999999999</v>
-      </c>
-      <c r="D930">
-        <v>4.4155158999999999</v>
-      </c>
-    </row>
-    <row r="931" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A931" s="1">
-        <v>45857</v>
-      </c>
-      <c r="B931">
-        <v>6296.79</v>
-      </c>
-      <c r="C931">
-        <v>98.481999999999999</v>
-      </c>
-      <c r="D931">
-        <v>4.4155158999999999</v>
-      </c>
-    </row>
-    <row r="932" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A932" s="1">
-        <v>45858</v>
-      </c>
-      <c r="B932">
-        <v>6296.79</v>
-      </c>
-      <c r="C932">
-        <v>98.481999999999999</v>
-      </c>
-      <c r="D932">
-        <v>4.4155158999999999</v>
-      </c>
-    </row>
-    <row r="933" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A933" s="1">
-        <v>45859</v>
-      </c>
-      <c r="B933">
-        <v>6305.6</v>
-      </c>
-      <c r="C933">
-        <v>97.852999999999994</v>
-      </c>
-      <c r="D933">
-        <v>4.3777265549999997</v>
-      </c>
-    </row>
-    <row r="934" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A934" s="1">
-        <v>45860</v>
-      </c>
-      <c r="B934">
-        <v>6309.62</v>
-      </c>
-      <c r="C934">
-        <v>97.392009999999999</v>
-      </c>
-      <c r="D934">
-        <v>4.3440170289999998</v>
-      </c>
-    </row>
-    <row r="935" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A935" s="1">
-        <v>45861</v>
-      </c>
-      <c r="B935">
-        <v>6358.91</v>
-      </c>
-      <c r="C935">
-        <v>97.213999999999999</v>
-      </c>
-      <c r="D935">
-        <v>4.3797640800000002</v>
-      </c>
-    </row>
-    <row r="936" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A936" s="1">
-        <v>45862</v>
-      </c>
-      <c r="B936">
-        <v>6363.35</v>
-      </c>
-      <c r="C936">
-        <v>97.377009999999999</v>
-      </c>
-      <c r="D936">
-        <v>4.3957114219999998</v>
-      </c>
-    </row>
-    <row r="937" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A937" s="1">
-        <v>45863</v>
-      </c>
-      <c r="B937">
-        <v>6388.64</v>
-      </c>
-      <c r="C937">
-        <v>97.644999999999996</v>
-      </c>
-      <c r="D937">
-        <v>4.3878297809999998</v>
-      </c>
-    </row>
-    <row r="938" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A938" s="1">
-        <v>45864</v>
-      </c>
-      <c r="B938">
-        <v>6388.64</v>
-      </c>
-      <c r="C938">
-        <v>97.644999999999996</v>
-      </c>
-      <c r="D938">
-        <v>4.3878297809999998</v>
-      </c>
-    </row>
-    <row r="939" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A939" s="1">
-        <v>45865</v>
-      </c>
-      <c r="B939">
-        <v>6388.64</v>
-      </c>
-      <c r="C939">
-        <v>97.644999999999996</v>
-      </c>
-      <c r="D939">
-        <v>4.3878297809999998</v>
-      </c>
-    </row>
-    <row r="940" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A940" s="1">
-        <v>45866</v>
-      </c>
-      <c r="B940">
-        <v>6389.77</v>
-      </c>
-      <c r="C940">
-        <v>98.634</v>
-      </c>
-      <c r="D940">
-        <v>4.4097924229999999</v>
-      </c>
-    </row>
-    <row r="941" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A941" s="1">
-        <v>45867</v>
-      </c>
-      <c r="B941">
-        <v>6370.86</v>
-      </c>
-      <c r="C941">
-        <v>98.885999999999996</v>
-      </c>
-      <c r="D941">
-        <v>4.3203558920000003</v>
-      </c>
-    </row>
-    <row r="942" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A942" s="1">
-        <v>45868</v>
-      </c>
-      <c r="B942">
-        <v>6362.9</v>
-      </c>
-      <c r="C942">
-        <v>99.814999999999998</v>
-      </c>
-      <c r="D942">
-        <v>4.3699922559999997</v>
-      </c>
-    </row>
-    <row r="943" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A943" s="1">
-        <v>45869</v>
-      </c>
-      <c r="B943">
-        <v>6339.39</v>
-      </c>
-      <c r="C943">
-        <v>99.968000000000004</v>
-      </c>
-      <c r="D943">
-        <v>4.3739976880000002</v>
-      </c>
-    </row>
-    <row r="944" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A944" s="1">
-        <v>45870</v>
-      </c>
-      <c r="B944">
-        <v>6238.01</v>
-      </c>
-      <c r="C944">
-        <v>99.141009999999994</v>
-      </c>
-      <c r="D944">
-        <v>4.2158885000000001</v>
-      </c>
-    </row>
-    <row r="945" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A945" s="1">
-        <v>45871</v>
-      </c>
-      <c r="B945">
-        <v>6238.01</v>
-      </c>
-      <c r="C945">
-        <v>99.141009999999994</v>
-      </c>
-      <c r="D945">
-        <v>4.2158885000000001</v>
-      </c>
-    </row>
-    <row r="946" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A946" s="1">
-        <v>45872</v>
-      </c>
-      <c r="B946">
-        <v>6238.01</v>
-      </c>
-      <c r="C946">
-        <v>99.141009999999994</v>
-      </c>
-      <c r="D946">
-        <v>4.2158885000000001</v>
-      </c>
-    </row>
-    <row r="947" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A947" s="1">
-        <v>45873</v>
-      </c>
-      <c r="B947">
-        <v>6329.94</v>
-      </c>
-      <c r="C947">
-        <v>98.784000000000006</v>
-      </c>
-      <c r="D947">
-        <v>4.1923475269999999</v>
-      </c>
-    </row>
-    <row r="948" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A948" s="1">
-        <v>45874</v>
-      </c>
-      <c r="B948">
-        <v>6299.19</v>
-      </c>
-      <c r="C948">
-        <v>98.78201</v>
-      </c>
-      <c r="D948">
-        <v>4.2099809649999997</v>
-      </c>
-    </row>
-    <row r="949" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A949" s="1">
-        <v>45875</v>
-      </c>
-      <c r="B949">
-        <v>6345.06</v>
-      </c>
-      <c r="C949">
-        <v>98.177000000000007</v>
-      </c>
-      <c r="D949">
-        <v>4.2256851199999996</v>
-      </c>
-    </row>
-    <row r="950" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A950" s="1">
-        <v>45876</v>
-      </c>
-      <c r="B950">
-        <v>6340</v>
-      </c>
-      <c r="C950">
-        <v>98.4</v>
-      </c>
-      <c r="D950">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="951" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A951" s="1">
-        <v>45877</v>
-      </c>
-      <c r="B951">
-        <v>6389.45</v>
-      </c>
-      <c r="C951">
-        <v>98.180009999999996</v>
-      </c>
-      <c r="D951">
-        <v>4.2829351429999996</v>
-      </c>
-    </row>
-    <row r="952" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A952" s="1">
-        <v>45878</v>
-      </c>
-      <c r="B952">
-        <v>6389.45</v>
-      </c>
-      <c r="C952">
-        <v>98.180009999999996</v>
-      </c>
-      <c r="D952">
-        <v>4.2829351429999996</v>
-      </c>
-    </row>
-    <row r="953" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A953" s="1">
-        <v>45879</v>
-      </c>
-      <c r="B953">
-        <v>6389.45</v>
-      </c>
-      <c r="C953">
-        <v>98.180009999999996</v>
-      </c>
-      <c r="D953">
-        <v>4.2829351429999996</v>
-      </c>
-    </row>
-    <row r="954" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A954" s="1">
-        <v>45880</v>
-      </c>
-      <c r="B954">
-        <v>6373.45</v>
-      </c>
-      <c r="C954">
-        <v>98.52</v>
-      </c>
-      <c r="D954">
-        <v>4.2848758699999996</v>
-      </c>
-    </row>
-    <row r="955" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A955" s="1">
-        <v>45881</v>
-      </c>
-      <c r="B955">
-        <v>6445.76</v>
-      </c>
-      <c r="C955">
-        <v>98.097009999999997</v>
-      </c>
-      <c r="D955">
-        <v>4.2887582780000004</v>
-      </c>
-    </row>
-    <row r="956" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A956" s="1">
-        <v>45882</v>
-      </c>
-      <c r="B956">
-        <v>6466.58</v>
-      </c>
-      <c r="C956">
-        <v>97.84</v>
-      </c>
-      <c r="D956">
-        <v>4.2326059340000004</v>
-      </c>
-    </row>
-    <row r="957" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A957" s="1">
-        <v>45883</v>
-      </c>
-      <c r="B957">
-        <v>6468.54</v>
-      </c>
-      <c r="C957">
-        <v>98.254009999999994</v>
-      </c>
-      <c r="D957">
-        <v>4.2848758699999996</v>
-      </c>
-    </row>
-    <row r="958" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A958" s="1">
-        <v>45884</v>
-      </c>
-      <c r="B958">
-        <v>6449.8</v>
-      </c>
-      <c r="C958">
-        <v>97.852010000000007</v>
-      </c>
-      <c r="D958">
-        <v>4.315972328</v>
-      </c>
-    </row>
-    <row r="959" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A959" s="1">
-        <v>45885</v>
-      </c>
-      <c r="B959">
-        <v>6449.8</v>
-      </c>
-      <c r="C959">
-        <v>97.852010000000007</v>
-      </c>
-      <c r="D959">
-        <v>4.315972328</v>
-      </c>
-    </row>
-    <row r="960" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A960" s="1">
-        <v>45886</v>
-      </c>
-      <c r="B960">
-        <v>6449.8</v>
-      </c>
-      <c r="C960">
-        <v>97.852010000000007</v>
-      </c>
-      <c r="D960">
-        <v>4.315972328</v>
-      </c>
-    </row>
-    <row r="961" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A961" s="1">
-        <v>45887</v>
-      </c>
-      <c r="B961">
-        <v>6449.15</v>
-      </c>
-      <c r="C961">
-        <v>98.167010000000005</v>
-      </c>
-      <c r="D961">
-        <v>4.3335208889999999</v>
-      </c>
-    </row>
-    <row r="962" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A962" s="1">
-        <v>45888</v>
-      </c>
-      <c r="B962">
-        <v>6411.37</v>
-      </c>
-      <c r="C962">
-        <v>98.265010000000004</v>
-      </c>
-      <c r="D962">
-        <v>4.3062334059999996</v>
-      </c>
-    </row>
-    <row r="963" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A963" s="1">
-        <v>45889</v>
-      </c>
-      <c r="B963">
-        <v>6395.78</v>
-      </c>
-      <c r="C963">
-        <v>98.218000000000004</v>
-      </c>
-      <c r="D963">
-        <v>4.2906646730000002</v>
-      </c>
-    </row>
-    <row r="964" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A964" s="1">
-        <v>45890</v>
-      </c>
-      <c r="B964">
-        <v>6370.17</v>
-      </c>
-      <c r="C964">
-        <v>98.619</v>
-      </c>
-      <c r="D964">
-        <v>4.3276758190000004</v>
-      </c>
-    </row>
-    <row r="965" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A965" s="1">
-        <v>45891</v>
-      </c>
-      <c r="B965">
-        <v>6466.91</v>
-      </c>
-      <c r="C965">
-        <v>97.715999999999994</v>
-      </c>
-      <c r="D965">
-        <v>4.2537355420000003</v>
-      </c>
-    </row>
-    <row r="966" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A966" s="1">
-        <v>45892</v>
-      </c>
-      <c r="B966">
-        <v>6466.91</v>
-      </c>
-      <c r="C966">
-        <v>97.715999999999994</v>
-      </c>
-      <c r="D966">
-        <v>4.2537355420000003</v>
-      </c>
-    </row>
-    <row r="967" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A967" s="1">
-        <v>45893</v>
-      </c>
-      <c r="B967">
-        <v>6466.91</v>
-      </c>
-      <c r="C967">
-        <v>97.715999999999994</v>
-      </c>
-      <c r="D967">
-        <v>4.2537355420000003</v>
-      </c>
-    </row>
-    <row r="968" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A968" s="1">
-        <v>45894</v>
-      </c>
-      <c r="B968">
-        <v>6439.32</v>
-      </c>
-      <c r="C968">
-        <v>98.430009999999996</v>
-      </c>
-      <c r="D968">
-        <v>4.2750806810000004</v>
-      </c>
-    </row>
-    <row r="969" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A969" s="1">
-        <v>45895</v>
-      </c>
-      <c r="B969">
-        <v>6465.94</v>
-      </c>
-      <c r="C969">
-        <v>98.225009999999997</v>
-      </c>
-      <c r="D969">
-        <v>4.2614736559999997</v>
-      </c>
-    </row>
-    <row r="970" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A970" s="1">
-        <v>45896</v>
-      </c>
-      <c r="B970">
-        <v>6481.4</v>
-      </c>
-      <c r="C970">
-        <v>98.231999999999999</v>
-      </c>
-      <c r="D970">
-        <v>4.2343130110000002</v>
-      </c>
-    </row>
-    <row r="971" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A971" s="1">
-        <v>45897</v>
-      </c>
-      <c r="B971">
-        <v>6501.86</v>
-      </c>
-      <c r="C971">
-        <v>97.813000000000002</v>
-      </c>
-      <c r="D971">
-        <v>4.2033472060000001</v>
-      </c>
-    </row>
-    <row r="972" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A972" s="1">
-        <v>45898</v>
-      </c>
-      <c r="B972">
-        <v>6460.26</v>
-      </c>
-      <c r="C972">
-        <v>97.771000000000001</v>
-      </c>
-      <c r="D972">
-        <v>4.2284183500000001</v>
-      </c>
-    </row>
-    <row r="973" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A973" s="1">
-        <v>45899</v>
-      </c>
-      <c r="B973">
-        <v>6460.26</v>
-      </c>
-      <c r="C973">
-        <v>97.771000000000001</v>
-      </c>
-      <c r="D973">
-        <v>4.2284183500000001</v>
-      </c>
-    </row>
-    <row r="974" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A974" s="1">
-        <v>45900</v>
-      </c>
-      <c r="B974">
-        <v>6460.26</v>
-      </c>
-      <c r="C974">
-        <v>97.771000000000001</v>
-      </c>
-      <c r="D974">
-        <v>4.2284183500000001</v>
-      </c>
-    </row>
-    <row r="975" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A975" s="1">
-        <v>45901</v>
-      </c>
-      <c r="B975">
-        <v>6460.26</v>
-      </c>
-      <c r="C975">
-        <v>97.771000000000001</v>
-      </c>
-      <c r="D975">
-        <v>4.2284183500000001</v>
-      </c>
-    </row>
-    <row r="976" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A976" s="1">
-        <v>45902</v>
-      </c>
-      <c r="B976">
-        <v>6415.54</v>
-      </c>
-      <c r="C976">
-        <v>98.397000000000006</v>
-      </c>
-      <c r="D976">
-        <v>4.2614030840000003</v>
-      </c>
-    </row>
-    <row r="977" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A977" s="1">
-        <v>45903</v>
-      </c>
-      <c r="B977">
-        <v>6448.26</v>
-      </c>
-      <c r="C977">
-        <v>98.142009999999999</v>
-      </c>
-      <c r="D977">
-        <v>4.2167596820000002</v>
-      </c>
-    </row>
-    <row r="978" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A978" s="1">
-        <v>45904</v>
-      </c>
-      <c r="B978">
-        <v>6502.08</v>
-      </c>
-      <c r="C978">
-        <v>98.347009999999997</v>
-      </c>
-      <c r="D978">
-        <v>4.1607198719999996</v>
-      </c>
-    </row>
-    <row r="979" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A979" s="1">
-        <v>45905</v>
-      </c>
-      <c r="B979">
-        <v>6481.5</v>
-      </c>
-      <c r="C979">
-        <v>97.768010000000004</v>
-      </c>
-      <c r="D979">
-        <v>4.0742330549999997</v>
-      </c>
-    </row>
-    <row r="980" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A980" s="1">
-        <v>45906</v>
-      </c>
-      <c r="B980">
-        <v>6481.5</v>
-      </c>
-      <c r="C980">
-        <v>97.768010000000004</v>
-      </c>
-      <c r="D980">
-        <v>4.0742330549999997</v>
-      </c>
-    </row>
-    <row r="981" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A981" s="1">
-        <v>45907</v>
-      </c>
-      <c r="B981">
-        <v>6481.5</v>
-      </c>
-      <c r="C981">
-        <v>97.768010000000004</v>
-      </c>
-      <c r="D981">
-        <v>4.0742330549999997</v>
-      </c>
-    </row>
-    <row r="982" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A982" s="1">
-        <v>45908</v>
-      </c>
-      <c r="B982">
-        <v>6495.15</v>
-      </c>
-      <c r="C982">
-        <v>97.453999999999994</v>
-      </c>
-      <c r="D982">
-        <v>4.0398168559999998</v>
-      </c>
-    </row>
-    <row r="983" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A983" s="1">
-        <v>45909</v>
-      </c>
-      <c r="B983">
-        <v>6512.61</v>
-      </c>
-      <c r="C983">
-        <v>97.787999999999997</v>
-      </c>
-      <c r="D983">
-        <v>4.0875329970000003</v>
-      </c>
-    </row>
-    <row r="984" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A984" s="1">
-        <v>45910</v>
-      </c>
-      <c r="B984">
-        <v>6532.04</v>
-      </c>
-      <c r="C984">
-        <v>97.780010000000004</v>
-      </c>
-      <c r="D984">
-        <v>4.0454263690000003</v>
-      </c>
-    </row>
-    <row r="985" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A985" s="1">
-        <v>45911</v>
-      </c>
-      <c r="B985">
-        <v>6587.47</v>
-      </c>
-      <c r="C985">
-        <v>97.531009999999995</v>
-      </c>
-      <c r="D985">
-        <v>4.0205907820000002</v>
-      </c>
-    </row>
-    <row r="986" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A986" s="1">
-        <v>45912</v>
-      </c>
-      <c r="B986">
-        <v>6584.29</v>
-      </c>
-      <c r="C986">
-        <v>97.55</v>
-      </c>
-      <c r="D986">
-        <v>4.064320564</v>
-      </c>
-    </row>
-    <row r="987" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A987" s="1">
-        <v>45913</v>
-      </c>
-      <c r="B987">
-        <v>6584.29</v>
-      </c>
-      <c r="C987">
-        <v>97.55</v>
-      </c>
-      <c r="D987">
-        <v>4.064320564</v>
-      </c>
-    </row>
-    <row r="988" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A988" s="1">
-        <v>45914</v>
-      </c>
-      <c r="B988">
-        <v>6584.29</v>
-      </c>
-      <c r="C988">
-        <v>97.55</v>
-      </c>
-      <c r="D988">
-        <v>4.064320564</v>
-      </c>
-    </row>
-    <row r="989" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A989" s="1">
-        <v>45915</v>
-      </c>
-      <c r="B989">
-        <v>6615.28</v>
-      </c>
-      <c r="C989">
-        <v>97.302000000000007</v>
-      </c>
-      <c r="D989">
-        <v>4.0375146869999998</v>
-      </c>
-    </row>
-    <row r="990" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A990" s="1">
-        <v>45916</v>
-      </c>
-      <c r="B990">
-        <v>6606.76</v>
-      </c>
-      <c r="C990">
-        <v>96.632999999999996</v>
-      </c>
-      <c r="D990">
-        <v>4.0279178619999998</v>
-      </c>
-    </row>
-    <row r="991" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A991" s="1">
-        <v>45917</v>
-      </c>
-      <c r="B991">
-        <v>6600.35</v>
-      </c>
-      <c r="C991">
-        <v>96.873000000000005</v>
-      </c>
-      <c r="D991">
-        <v>4.0871677399999999</v>
-      </c>
-    </row>
-    <row r="992" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A992" s="1">
-        <v>45918</v>
-      </c>
-      <c r="B992">
-        <v>6631.96</v>
-      </c>
-      <c r="C992">
-        <v>97.348010000000002</v>
-      </c>
-      <c r="D992">
-        <v>4.1044082639999999</v>
-      </c>
-    </row>
-    <row r="993" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A993" s="1">
-        <v>45919</v>
-      </c>
-      <c r="B993">
-        <v>6664.36</v>
-      </c>
-      <c r="C993">
-        <v>97.644000000000005</v>
-      </c>
-      <c r="D993">
-        <v>4.1273927690000001</v>
-      </c>
-    </row>
-    <row r="994" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A994" s="1">
-        <v>45920</v>
-      </c>
-      <c r="B994">
-        <v>6664.36</v>
-      </c>
-      <c r="C994">
-        <v>97.644000000000005</v>
-      </c>
-      <c r="D994">
-        <v>4.1273927690000001</v>
-      </c>
-    </row>
-    <row r="995" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A995" s="1">
-        <v>45921</v>
-      </c>
-      <c r="B995">
-        <v>6664.36</v>
-      </c>
-      <c r="C995">
-        <v>97.644000000000005</v>
-      </c>
-      <c r="D995">
-        <v>4.1273927690000001</v>
-      </c>
-    </row>
-    <row r="996" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A996" s="1">
-        <v>45922</v>
-      </c>
-      <c r="B996">
-        <v>6693.75</v>
-      </c>
-      <c r="C996">
-        <v>97.340999999999994</v>
-      </c>
-      <c r="D996">
-        <v>4.1466560360000004</v>
-      </c>
-    </row>
-    <row r="997" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A997" s="1">
-        <v>45923</v>
-      </c>
-      <c r="B997">
-        <v>6656.92</v>
-      </c>
-      <c r="C997">
-        <v>97.264009999999999</v>
-      </c>
-      <c r="D997">
-        <v>4.1061286929999996</v>
-      </c>
-    </row>
-    <row r="998" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A998" s="1">
-        <v>45924</v>
-      </c>
-      <c r="B998">
-        <v>6637.97</v>
-      </c>
-      <c r="C998">
-        <v>97.873000000000005</v>
-      </c>
-      <c r="D998">
-        <v>4.146593094</v>
-      </c>
-    </row>
-    <row r="999" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A999" s="1">
-        <v>45925</v>
-      </c>
-      <c r="B999">
-        <v>6604.72</v>
-      </c>
-      <c r="C999">
-        <v>98.552999999999997</v>
-      </c>
-      <c r="D999">
-        <v>4.1697835919999999</v>
-      </c>
-    </row>
-    <row r="1000" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1000" s="1">
-        <v>45926</v>
-      </c>
-      <c r="B1000">
-        <v>6643.7</v>
-      </c>
-      <c r="C1000">
-        <v>98.152010000000004</v>
-      </c>
-      <c r="D1000">
-        <v>4.1755237579999998</v>
-      </c>
-    </row>
-    <row r="1001" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1001" s="1">
-        <v>45927</v>
-      </c>
-      <c r="B1001">
-        <v>6643.7</v>
-      </c>
-      <c r="C1001">
-        <v>98.152010000000004</v>
-      </c>
-      <c r="D1001">
-        <v>4.1755237579999998</v>
-      </c>
-    </row>
-    <row r="1002" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1002" s="1">
-        <v>45928</v>
-      </c>
-      <c r="B1002">
-        <v>6643.7</v>
-      </c>
-      <c r="C1002">
-        <v>98.152010000000004</v>
-      </c>
-      <c r="D1002">
-        <v>4.1755237579999998</v>
-      </c>
-    </row>
-    <row r="1003" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1003" s="1">
-        <v>45929</v>
-      </c>
-      <c r="B1003">
-        <v>6661.21</v>
-      </c>
-      <c r="C1003">
-        <v>97.906009999999995</v>
-      </c>
-      <c r="D1003">
-        <v>4.1387042999999997</v>
-      </c>
-    </row>
-    <row r="1004" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1004" s="1">
-        <v>45930</v>
-      </c>
-      <c r="B1004">
-        <v>6688.46</v>
-      </c>
-      <c r="C1004">
-        <v>97.775000000000006</v>
-      </c>
-      <c r="D1004">
-        <v>4.1502799990000003</v>
-      </c>
-    </row>
-    <row r="1005" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1005" s="1">
-        <v>45931</v>
-      </c>
-      <c r="B1005">
-        <v>6711.2</v>
-      </c>
-      <c r="C1005">
-        <v>97.706000000000003</v>
-      </c>
-      <c r="D1005">
-        <v>4.0981035229999998</v>
-      </c>
-    </row>
-    <row r="1006" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1006" s="1">
-        <v>45932</v>
-      </c>
-      <c r="B1006">
-        <v>6715.35</v>
-      </c>
-      <c r="C1006">
-        <v>97.846010000000007</v>
-      </c>
-      <c r="D1006">
-        <v>4.0826578140000001</v>
-      </c>
-    </row>
-    <row r="1007" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1007" s="1">
-        <v>45933</v>
-      </c>
-      <c r="B1007">
-        <v>6715.79</v>
-      </c>
-      <c r="C1007">
-        <v>97.723010000000002</v>
-      </c>
-      <c r="D1007">
-        <v>4.1191749570000002</v>
-      </c>
-    </row>
-    <row r="1008" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1008" s="1">
-        <v>45934</v>
-      </c>
-      <c r="B1008">
-        <v>6715.79</v>
-      </c>
-      <c r="C1008">
-        <v>97.723010000000002</v>
-      </c>
-      <c r="D1008">
-        <v>4.1191749570000002</v>
-      </c>
-    </row>
-    <row r="1009" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1009" s="1">
-        <v>45935</v>
-      </c>
-      <c r="B1009">
-        <v>6715.79</v>
-      </c>
-      <c r="C1009">
-        <v>97.723010000000002</v>
-      </c>
-      <c r="D1009">
-        <v>4.1191749570000002</v>
-      </c>
-    </row>
-    <row r="1010" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1010" s="1">
-        <v>45936</v>
-      </c>
-      <c r="B1010">
-        <v>6740.28</v>
-      </c>
-      <c r="C1010">
-        <v>98.108000000000004</v>
-      </c>
-      <c r="D1010">
-        <v>4.1520452499999996</v>
-      </c>
-    </row>
-    <row r="1011" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1011" s="1">
-        <v>45937</v>
-      </c>
-      <c r="B1011">
-        <v>6714.59</v>
-      </c>
-      <c r="C1011">
-        <v>98.578000000000003</v>
-      </c>
-      <c r="D1011">
-        <v>4.1229705809999997</v>
-      </c>
-    </row>
-    <row r="1012" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1012" s="1">
-        <v>45938</v>
-      </c>
-      <c r="B1012">
-        <v>6753.72</v>
-      </c>
-      <c r="C1012">
-        <v>98.915000000000006</v>
-      </c>
-      <c r="D1012">
-        <v>4.1171360019999996</v>
-      </c>
-    </row>
-    <row r="1013" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1013" s="1">
-        <v>45939</v>
-      </c>
-      <c r="B1013">
-        <v>6735.11</v>
-      </c>
-      <c r="C1013">
-        <v>99.537999999999997</v>
-      </c>
-      <c r="D1013">
-        <v>4.1383914949999996</v>
-      </c>
-    </row>
-    <row r="1014" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1014" s="1">
-        <v>45940</v>
-      </c>
-      <c r="B1014">
-        <v>6552.51</v>
-      </c>
-      <c r="C1014">
-        <v>98.977999999999994</v>
-      </c>
-      <c r="D1014">
-        <v>4.0321502689999997</v>
-      </c>
-    </row>
-    <row r="1015" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1015" s="1">
-        <v>45941</v>
-      </c>
-      <c r="B1015">
-        <v>6552.51</v>
-      </c>
-      <c r="C1015">
-        <v>98.977999999999994</v>
-      </c>
-      <c r="D1015">
-        <v>4.0321502689999997</v>
-      </c>
-    </row>
-    <row r="1016" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1016" s="1">
-        <v>45942</v>
-      </c>
-      <c r="B1016">
-        <v>6552.51</v>
-      </c>
-      <c r="C1016">
-        <v>98.977999999999994</v>
-      </c>
-      <c r="D1016">
-        <v>4.0321502689999997</v>
-      </c>
-    </row>
-    <row r="1017" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1017" s="1">
-        <v>45943</v>
-      </c>
-      <c r="B1017">
-        <v>6654.72</v>
-      </c>
-      <c r="C1017">
-        <v>99.269000000000005</v>
-      </c>
-      <c r="D1017">
-        <v>4.0321502689999997</v>
-      </c>
-    </row>
-    <row r="1018" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1018" s="1">
-        <v>45944</v>
-      </c>
-      <c r="B1018">
-        <v>6644.31</v>
-      </c>
-      <c r="C1018">
-        <v>99.046999999999997</v>
-      </c>
-      <c r="D1018">
-        <v>4.0320959089999997</v>
-      </c>
-    </row>
-    <row r="1019" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1019" s="1">
-        <v>45945</v>
-      </c>
-      <c r="B1019">
-        <v>6671.06</v>
-      </c>
-      <c r="C1019">
-        <v>98.793009999999995</v>
-      </c>
-      <c r="D1019">
-        <v>4.0282020569999997</v>
-      </c>
-    </row>
-    <row r="1020" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1020" s="1">
-        <v>45946</v>
-      </c>
-      <c r="B1020">
-        <v>6629.07</v>
-      </c>
-      <c r="C1020">
-        <v>98.336010000000002</v>
-      </c>
-      <c r="D1020">
-        <v>3.9745140079999999</v>
-      </c>
-    </row>
-    <row r="1021" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1021" s="1">
-        <v>45947</v>
-      </c>
-      <c r="B1021">
-        <v>6664.01</v>
-      </c>
-      <c r="C1021">
-        <v>98.433009999999996</v>
-      </c>
-      <c r="D1021">
-        <v>4.0087881090000002</v>
-      </c>
-    </row>
-    <row r="1022" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1022" s="1">
-        <v>45948</v>
-      </c>
-      <c r="B1022">
-        <v>6664.01</v>
-      </c>
-      <c r="C1022">
-        <v>98.433009999999996</v>
-      </c>
-      <c r="D1022">
-        <v>4.0087881090000002</v>
-      </c>
-    </row>
-    <row r="1023" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1023" s="1">
-        <v>45949</v>
-      </c>
-      <c r="B1023">
-        <v>6664.01</v>
-      </c>
-      <c r="C1023">
-        <v>98.433009999999996</v>
-      </c>
-      <c r="D1023">
-        <v>4.0087881090000002</v>
-      </c>
-    </row>
-    <row r="1024" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1024" s="1">
-        <v>45950</v>
-      </c>
-      <c r="B1024">
-        <v>6735.13</v>
-      </c>
-      <c r="C1024">
-        <v>98.586010000000002</v>
-      </c>
-      <c r="D1024">
-        <v>3.9799900049999999</v>
-      </c>
-    </row>
-    <row r="1025" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1025" s="1">
-        <v>45951</v>
-      </c>
-      <c r="B1025">
-        <v>6735.35</v>
-      </c>
-      <c r="C1025">
-        <v>98.934010000000001</v>
-      </c>
-      <c r="D1025">
-        <v>3.962716103</v>
-      </c>
-    </row>
-    <row r="1026" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1026" s="1">
-        <v>45952</v>
-      </c>
-      <c r="B1026">
-        <v>6699.4</v>
-      </c>
-      <c r="C1026">
-        <v>98.897000000000006</v>
-      </c>
-      <c r="D1026">
-        <v>3.949278831</v>
-      </c>
-    </row>
-    <row r="1027" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1027" s="1">
-        <v>45953</v>
-      </c>
-      <c r="B1027">
-        <v>6738.44</v>
-      </c>
-      <c r="C1027">
-        <v>98.936000000000007</v>
-      </c>
-      <c r="D1027">
-        <v>4.0008800000000004</v>
-      </c>
-    </row>
-    <row r="1028" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1028" s="1">
-        <v>45954</v>
-      </c>
-      <c r="B1028">
-        <v>6791.69</v>
-      </c>
-      <c r="C1028">
-        <v>98.951999999999998</v>
-      </c>
-      <c r="D1028">
-        <v>4.0007029999999997</v>
-      </c>
-    </row>
-    <row r="1029" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1029" s="1">
-        <v>45955</v>
-      </c>
-      <c r="B1029">
-        <v>6791.69</v>
-      </c>
-      <c r="C1029">
-        <v>98.951999999999998</v>
-      </c>
-      <c r="D1029">
-        <v>4.0007029999999997</v>
-      </c>
-    </row>
-    <row r="1030" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1030" s="1">
-        <v>45956</v>
-      </c>
-      <c r="B1030">
-        <v>6791.69</v>
-      </c>
-      <c r="C1030">
-        <v>98.951999999999998</v>
-      </c>
-      <c r="D1030">
-        <v>4.0007029999999997</v>
-      </c>
-    </row>
-    <row r="1031" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1031" s="1">
-        <v>45957</v>
-      </c>
-      <c r="B1031">
-        <v>6875.16</v>
-      </c>
-      <c r="C1031">
-        <v>98.783000000000001</v>
-      </c>
-      <c r="D1031">
-        <v>3.979543686</v>
-      </c>
-    </row>
-    <row r="1032" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1032" s="1">
-        <v>45958</v>
-      </c>
-      <c r="B1032">
-        <v>6890.89</v>
-      </c>
-      <c r="C1032">
-        <v>98.667010000000005</v>
-      </c>
-      <c r="D1032">
-        <v>3.9756469729999999</v>
-      </c>
-    </row>
-    <row r="1033" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1033" s="1">
-        <v>45959</v>
-      </c>
-      <c r="B1033">
-        <v>6890.59</v>
-      </c>
-      <c r="C1033">
-        <v>99.22</v>
-      </c>
-      <c r="D1033">
-        <v>4.0757141109999999</v>
-      </c>
-    </row>
-    <row r="1034" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1034" s="1">
-        <v>45960</v>
-      </c>
-      <c r="B1034">
-        <v>6822.34</v>
-      </c>
-      <c r="C1034">
-        <v>99.525999999999996</v>
-      </c>
-      <c r="D1034">
-        <v>4.096981049</v>
-      </c>
-    </row>
-    <row r="1035" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1035" s="1">
-        <v>45961</v>
-      </c>
-      <c r="B1035">
-        <v>6840.2</v>
-      </c>
-      <c r="C1035">
-        <v>99.804010000000005</v>
-      </c>
-      <c r="D1035">
-        <v>4.0774850850000002</v>
-      </c>
-    </row>
-    <row r="1036" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1036" s="1">
-        <v>45962</v>
-      </c>
-      <c r="B1036">
-        <v>6840.2</v>
-      </c>
-      <c r="C1036">
-        <v>99.804010000000005</v>
-      </c>
-      <c r="D1036">
-        <v>4.0774850850000002</v>
-      </c>
-    </row>
-    <row r="1037" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1037" s="1">
-        <v>45963</v>
-      </c>
-      <c r="B1037">
-        <v>6840.2</v>
-      </c>
-      <c r="C1037">
-        <v>99.804010000000005</v>
-      </c>
-      <c r="D1037">
-        <v>4.0774850850000002</v>
-      </c>
-    </row>
-    <row r="1038" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1038" s="1">
-        <v>45964</v>
-      </c>
-      <c r="B1038">
-        <v>6851.97</v>
-      </c>
-      <c r="C1038">
-        <v>99.873000000000005</v>
-      </c>
-      <c r="D1038">
-        <v>4.110429764</v>
-      </c>
-    </row>
-    <row r="1039" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1039" s="1">
-        <v>45965</v>
-      </c>
-      <c r="B1039">
-        <v>6771.55</v>
-      </c>
-      <c r="C1039">
-        <v>100.224</v>
-      </c>
-      <c r="D1039">
-        <v>4.0851583480000002</v>
-      </c>
-    </row>
-    <row r="1040" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1040" s="1">
-        <v>45966</v>
-      </c>
-      <c r="B1040">
-        <v>6796.29</v>
-      </c>
-      <c r="C1040">
-        <v>100.20399999999999</v>
-      </c>
-      <c r="D1040">
-        <v>4.1590785979999998</v>
-      </c>
-    </row>
-    <row r="1041" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1041" s="1">
-        <v>45967</v>
-      </c>
-      <c r="B1041">
-        <v>6720.32</v>
-      </c>
-      <c r="C1041">
-        <v>99.733000000000004</v>
-      </c>
-      <c r="D1041">
-        <v>4.0831413269999999</v>
-      </c>
-    </row>
-    <row r="1042" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1042" s="1">
-        <v>45968</v>
-      </c>
-      <c r="B1042">
-        <v>6728.8</v>
-      </c>
-      <c r="C1042">
-        <v>99.602999999999994</v>
-      </c>
-      <c r="D1042">
-        <v>4.0966205599999999</v>
-      </c>
-    </row>
-    <row r="1043" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1043" s="1">
-        <v>45969</v>
-      </c>
-      <c r="B1043">
-        <v>6728.8</v>
-      </c>
-      <c r="C1043">
-        <v>99.602999999999994</v>
-      </c>
-      <c r="D1043">
-        <v>4.0966205599999999</v>
-      </c>
-    </row>
-    <row r="1044" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1044" s="1">
-        <v>45970</v>
-      </c>
-      <c r="B1044">
-        <v>6728.8</v>
-      </c>
-      <c r="C1044">
-        <v>99.602999999999994</v>
-      </c>
-      <c r="D1044">
-        <v>4.0966205599999999</v>
-      </c>
-    </row>
-    <row r="1045" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1045" s="1">
-        <v>45971</v>
-      </c>
-      <c r="B1045">
-        <v>6832.43</v>
-      </c>
-      <c r="C1045">
-        <v>99.588999999999999</v>
-      </c>
-      <c r="D1045">
-        <v>4.1160106660000002</v>
-      </c>
-    </row>
-    <row r="1046" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1046" s="1">
-        <v>45972</v>
-      </c>
-      <c r="B1046">
-        <v>6846.61</v>
-      </c>
-      <c r="C1046">
-        <v>99.443010000000001</v>
-      </c>
-      <c r="D1046">
-        <v>4.1160106660000002</v>
-      </c>
-    </row>
-    <row r="1047" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1047" s="1">
-        <v>45973</v>
-      </c>
-      <c r="B1047">
-        <v>6850.92</v>
-      </c>
-      <c r="C1047">
-        <v>99.495000000000005</v>
-      </c>
-      <c r="D1047">
-        <v>4.0693235400000001</v>
-      </c>
-    </row>
-    <row r="1048" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1048" s="1">
-        <v>45974</v>
-      </c>
-      <c r="B1048">
-        <v>6737.49</v>
-      </c>
-      <c r="C1048">
-        <v>99.156009999999995</v>
-      </c>
-      <c r="D1048">
-        <v>4.1191997530000002</v>
-      </c>
-    </row>
-    <row r="1049" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1049" s="1">
-        <v>45975</v>
-      </c>
-      <c r="B1049">
-        <v>6734.11</v>
-      </c>
-      <c r="C1049">
-        <v>99.299000000000007</v>
-      </c>
-      <c r="D1049">
-        <v>4.1482524869999997</v>
-      </c>
-    </row>
-    <row r="1050" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1050" s="1">
-        <v>45976</v>
-      </c>
-      <c r="B1050">
-        <v>6734.11</v>
-      </c>
-      <c r="C1050">
-        <v>99.299000000000007</v>
-      </c>
-      <c r="D1050">
-        <v>4.1482524869999997</v>
-      </c>
-    </row>
-    <row r="1051" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1051" s="1">
-        <v>45977</v>
-      </c>
-      <c r="B1051">
-        <v>6734.11</v>
-      </c>
-      <c r="C1051">
-        <v>99.299000000000007</v>
-      </c>
-      <c r="D1051">
-        <v>4.1482524869999997</v>
-      </c>
-    </row>
-    <row r="1052" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1052" s="1">
-        <v>45978</v>
-      </c>
-      <c r="B1052">
-        <v>6672.41</v>
-      </c>
-      <c r="C1052">
-        <v>99.588009999999997</v>
-      </c>
-      <c r="D1052">
-        <v>4.1385765079999999</v>
-      </c>
-    </row>
-    <row r="1053" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1053" s="1">
-        <v>45979</v>
-      </c>
-      <c r="B1053">
-        <v>6617.32</v>
-      </c>
-      <c r="C1053">
-        <v>99.55</v>
-      </c>
-      <c r="D1053">
-        <v>4.1134233470000003</v>
-      </c>
-    </row>
-    <row r="1054" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1054" s="1">
-        <v>45980</v>
-      </c>
-      <c r="B1054">
-        <v>6642.16</v>
-      </c>
-      <c r="C1054">
-        <v>100.22799999999999</v>
-      </c>
-      <c r="D1054">
-        <v>4.1366739270000004</v>
-      </c>
-    </row>
-    <row r="1055" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1055" s="1">
-        <v>45981</v>
-      </c>
-      <c r="B1055">
-        <v>6538.76</v>
-      </c>
-      <c r="C1055">
-        <v>100.158</v>
-      </c>
-      <c r="D1055">
-        <v>4.0844678879999998</v>
-      </c>
-    </row>
-    <row r="1056" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1056" s="1">
-        <v>45982</v>
-      </c>
-      <c r="B1056">
-        <v>6602.99</v>
-      </c>
-      <c r="C1056">
-        <v>100.18</v>
-      </c>
-      <c r="D1056">
-        <v>4.0632724759999999</v>
-      </c>
-    </row>
-    <row r="1057" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1057" s="1">
-        <v>45983</v>
-      </c>
-      <c r="B1057">
-        <v>6602.99</v>
-      </c>
-      <c r="C1057">
-        <v>100.18</v>
-      </c>
-      <c r="D1057">
-        <v>4.0632724759999999</v>
-      </c>
-    </row>
-    <row r="1058" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1058" s="1">
-        <v>45984</v>
-      </c>
-      <c r="B1058">
-        <v>6602.99</v>
-      </c>
-      <c r="C1058">
-        <v>100.18</v>
-      </c>
-      <c r="D1058">
-        <v>4.0632724759999999</v>
-      </c>
-    </row>
-    <row r="1059" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1059" s="1">
-        <v>45985</v>
-      </c>
-      <c r="B1059">
-        <v>6705.12</v>
-      </c>
-      <c r="C1059">
-        <v>100.142</v>
-      </c>
-      <c r="D1059">
-        <v>4.0248041150000002</v>
-      </c>
-    </row>
-    <row r="1060" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1060" s="1">
-        <v>45986</v>
-      </c>
-      <c r="B1060">
-        <v>6765.88</v>
-      </c>
-      <c r="C1060">
-        <v>99.664000000000001</v>
-      </c>
-      <c r="D1060">
-        <v>3.9960308069999999</v>
-      </c>
-    </row>
-    <row r="1061" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1061" s="1">
-        <v>45987</v>
-      </c>
-      <c r="B1061">
-        <v>6812.61</v>
-      </c>
-      <c r="C1061">
-        <v>99.594999999999999</v>
-      </c>
-      <c r="D1061">
-        <v>3.9940900799999999</v>
-      </c>
-    </row>
-    <row r="1062" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1062" s="1">
-        <v>45988</v>
-      </c>
-      <c r="B1062">
-        <v>6812.61</v>
-      </c>
-      <c r="C1062">
-        <v>99.536000000000001</v>
-      </c>
-      <c r="D1062">
-        <v>3.9940900799999999</v>
-      </c>
-    </row>
-    <row r="1063" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1063" s="1">
-        <v>45989</v>
-      </c>
-      <c r="B1063">
-        <v>6849.09</v>
-      </c>
-      <c r="C1063">
-        <v>99.459010000000006</v>
-      </c>
-      <c r="D1063">
-        <v>4.0132389069999999</v>
-      </c>
-    </row>
-    <row r="1064" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1064" s="1">
-        <v>45990</v>
-      </c>
-      <c r="B1064">
-        <v>6849.09</v>
-      </c>
-      <c r="C1064">
-        <v>99.459010000000006</v>
-      </c>
-      <c r="D1064">
-        <v>4.0132389069999999</v>
-      </c>
-    </row>
-    <row r="1065" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1065" s="1">
-        <v>45991</v>
-      </c>
-      <c r="B1065">
-        <v>6849.09</v>
-      </c>
-      <c r="C1065">
-        <v>99.459010000000006</v>
-      </c>
-      <c r="D1065">
-        <v>4.0132389069999999</v>
-      </c>
-    </row>
-    <row r="1066" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1066" s="1">
-        <v>45992</v>
-      </c>
-      <c r="B1066">
-        <v>6812.63</v>
-      </c>
-      <c r="C1066">
-        <v>99.414000000000001</v>
-      </c>
-      <c r="D1066">
-        <v>4.086480141</v>
-      </c>
-    </row>
-    <row r="1067" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1067" s="1">
-        <v>45993</v>
-      </c>
-      <c r="B1067">
-        <v>6829.37</v>
-      </c>
-      <c r="C1067">
-        <v>99.356999999999999</v>
-      </c>
-      <c r="D1067">
-        <v>4.0864887239999996</v>
-      </c>
-    </row>
-    <row r="1068" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1068" s="1">
-        <v>45994</v>
-      </c>
-      <c r="B1068">
-        <v>6849.72</v>
-      </c>
-      <c r="C1068">
-        <v>98.853999999999999</v>
-      </c>
-      <c r="D1068">
-        <v>4.0633001330000003</v>
-      </c>
-    </row>
-    <row r="1069" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1069" s="1">
-        <v>45995</v>
-      </c>
-      <c r="B1069">
-        <v>6857.12</v>
-      </c>
-      <c r="C1069">
-        <v>98.989009999999993</v>
-      </c>
-      <c r="D1069">
-        <v>4.098126411</v>
-      </c>
-    </row>
-    <row r="1070" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1070" s="1">
-        <v>45996</v>
-      </c>
-      <c r="B1070">
-        <v>6870.4</v>
-      </c>
-      <c r="C1070">
-        <v>98.992000000000004</v>
-      </c>
-      <c r="D1070">
-        <v>4.1350708010000004</v>
-      </c>
-    </row>
-    <row r="1071" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1071" s="1">
-        <v>45997</v>
-      </c>
-      <c r="B1071">
-        <v>6870.4</v>
-      </c>
-      <c r="C1071">
-        <v>98.992000000000004</v>
-      </c>
-      <c r="D1071">
-        <v>4.1350708010000004</v>
-      </c>
-    </row>
-    <row r="1072" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1072" s="1">
-        <v>45998</v>
-      </c>
-      <c r="B1072">
-        <v>6870.4</v>
-      </c>
-      <c r="C1072">
-        <v>98.992000000000004</v>
-      </c>
-      <c r="D1072">
-        <v>4.1350708010000004</v>
-      </c>
-    </row>
-    <row r="1073" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1073" s="1">
-        <v>45999</v>
-      </c>
-      <c r="B1073">
-        <v>6846.51</v>
-      </c>
-      <c r="C1073">
-        <v>99.087010000000006</v>
-      </c>
-      <c r="D1073">
-        <v>4.1643285749999999</v>
-      </c>
-    </row>
-    <row r="1074" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1074" s="1">
-        <v>46000</v>
-      </c>
-      <c r="B1074">
-        <v>6840.51</v>
-      </c>
-      <c r="C1074">
-        <v>99.22</v>
-      </c>
-      <c r="D1074">
-        <v>4.1878099439999996</v>
-      </c>
-    </row>
-    <row r="1075" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1075" s="1">
-        <v>46001</v>
-      </c>
-      <c r="B1075">
-        <v>6886.68</v>
-      </c>
-      <c r="C1075">
-        <v>98.786000000000001</v>
-      </c>
-      <c r="D1075">
-        <v>4.146821976</v>
-      </c>
-    </row>
-    <row r="1076" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1076" s="1">
-        <v>46002</v>
-      </c>
-      <c r="B1076">
-        <v>6901</v>
-      </c>
-      <c r="C1076">
-        <v>98.346010000000007</v>
-      </c>
-      <c r="D1076">
-        <v>4.1565999979999999</v>
-      </c>
-    </row>
-    <row r="1077" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1077" s="1">
-        <v>46003</v>
-      </c>
-      <c r="B1077">
-        <v>6827.41</v>
-      </c>
-      <c r="C1077">
-        <v>98.399000000000001</v>
-      </c>
-      <c r="D1077">
-        <v>4.1840562820000002</v>
-      </c>
-    </row>
-    <row r="1078" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1078" s="1">
-        <v>46004</v>
-      </c>
-      <c r="B1078">
-        <v>6827.41</v>
-      </c>
-      <c r="C1078">
-        <v>98.399000000000001</v>
-      </c>
-      <c r="D1078">
-        <v>4.1840562820000002</v>
-      </c>
-    </row>
-    <row r="1079" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1079" s="1">
-        <v>46005</v>
-      </c>
-      <c r="B1079">
-        <v>6827.41</v>
-      </c>
-      <c r="C1079">
-        <v>98.399000000000001</v>
-      </c>
-      <c r="D1079">
-        <v>4.1840562820000002</v>
-      </c>
-    </row>
-    <row r="1080" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1080" s="1">
-        <v>46006</v>
-      </c>
-      <c r="B1080">
-        <v>6816.51</v>
-      </c>
-      <c r="C1080">
-        <v>98.309010000000001</v>
-      </c>
-      <c r="D1080">
-        <v>4.1723432540000003</v>
-      </c>
-    </row>
-    <row r="1081" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1081" s="1">
-        <v>46007</v>
-      </c>
-      <c r="B1081">
-        <v>6800.26</v>
-      </c>
-      <c r="C1081">
-        <v>98.146000000000001</v>
-      </c>
-      <c r="D1081">
-        <v>4.1450128560000001</v>
-      </c>
-    </row>
-    <row r="1082" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1082" s="1">
-        <v>46008</v>
-      </c>
-      <c r="B1082">
-        <v>6721.43</v>
-      </c>
-      <c r="C1082">
-        <v>98.367999999999995</v>
-      </c>
-      <c r="D1082">
-        <v>4.1528482440000003</v>
-      </c>
-    </row>
-    <row r="1083" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1083" s="1">
-        <v>46009</v>
-      </c>
-      <c r="B1083">
-        <v>6774.76</v>
-      </c>
-      <c r="C1083">
-        <v>98.427000000000007</v>
-      </c>
-      <c r="D1083">
-        <v>4.1216554639999998</v>
-      </c>
-    </row>
-    <row r="1084" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1084" s="1">
-        <v>46010</v>
-      </c>
-      <c r="B1084">
-        <v>6834.5</v>
-      </c>
-      <c r="C1084">
-        <v>98.599010000000007</v>
-      </c>
-      <c r="D1084">
-        <v>4.1470880509999999</v>
-      </c>
-    </row>
-    <row r="1085" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1085" s="1">
-        <v>46011</v>
-      </c>
-      <c r="B1085">
-        <v>6834.5</v>
-      </c>
-      <c r="C1085">
-        <v>98.599010000000007</v>
-      </c>
-      <c r="D1085">
-        <v>4.1470880509999999</v>
-      </c>
-    </row>
-    <row r="1086" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1086" s="1">
-        <v>46012</v>
-      </c>
-      <c r="B1086">
-        <v>6834.5</v>
-      </c>
-      <c r="C1086">
-        <v>98.599010000000007</v>
-      </c>
-      <c r="D1086">
-        <v>4.1470880509999999</v>
-      </c>
-    </row>
-    <row r="1087" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1087" s="1">
-        <v>46013</v>
-      </c>
-      <c r="B1087">
-        <v>6878.49</v>
-      </c>
-      <c r="C1087">
-        <v>98.286000000000001</v>
-      </c>
-      <c r="D1087">
-        <v>4.1627635959999996</v>
-      </c>
-    </row>
-    <row r="1088" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1088" s="1">
-        <v>46014</v>
-      </c>
-      <c r="B1088">
-        <v>6909.79</v>
-      </c>
-      <c r="C1088">
-        <v>97.941999999999993</v>
-      </c>
-      <c r="D1088">
-        <v>4.1627922059999998</v>
-      </c>
-    </row>
-    <row r="1089" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1089" s="1">
-        <v>46015</v>
-      </c>
-      <c r="B1089">
-        <v>6932.05</v>
-      </c>
-      <c r="C1089">
-        <v>97.976010000000002</v>
-      </c>
-      <c r="D1089">
-        <v>4.1335067749999999</v>
-      </c>
-    </row>
-    <row r="1090" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1090" s="1">
-        <v>46016</v>
-      </c>
-      <c r="B1090">
-        <v>6932.05</v>
-      </c>
-      <c r="C1090">
-        <v>97.976010000000002</v>
-      </c>
-      <c r="D1090">
-        <v>4.1335067749999999</v>
-      </c>
-    </row>
-    <row r="1091" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1091" s="1">
-        <v>46017</v>
-      </c>
-      <c r="B1091">
-        <v>6929.94</v>
-      </c>
-      <c r="C1091">
-        <v>98.022000000000006</v>
-      </c>
-      <c r="D1091">
-        <v>4.1277122500000001</v>
-      </c>
-    </row>
-    <row r="1092" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1092" s="1">
-        <v>46018</v>
-      </c>
-      <c r="B1092">
-        <v>6929.94</v>
-      </c>
-      <c r="C1092">
-        <v>98.022000000000006</v>
-      </c>
-      <c r="D1092">
-        <v>4.1277122500000001</v>
-      </c>
-    </row>
-    <row r="1093" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1093" s="1">
-        <v>46019</v>
-      </c>
-      <c r="B1093">
-        <v>6929.94</v>
-      </c>
-      <c r="C1093">
-        <v>98.022000000000006</v>
-      </c>
-      <c r="D1093">
-        <v>4.1277122500000001</v>
-      </c>
-    </row>
-    <row r="1094" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1094" s="1">
-        <v>46020</v>
-      </c>
-      <c r="B1094">
-        <v>6905.74</v>
-      </c>
-      <c r="C1094">
-        <v>98.037000000000006</v>
-      </c>
-      <c r="D1094">
-        <v>4.1101617810000004</v>
-      </c>
-    </row>
-    <row r="1095" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1095" s="1">
-        <v>46021</v>
-      </c>
-      <c r="B1095">
-        <v>6896.24</v>
-      </c>
-      <c r="C1095">
-        <v>98.238010000000003</v>
-      </c>
-      <c r="D1095">
-        <v>4.1218948360000001</v>
-      </c>
-    </row>
-    <row r="1096" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1096" s="1">
-        <v>46022</v>
-      </c>
-      <c r="B1096">
-        <v>6845.5</v>
-      </c>
-      <c r="C1096">
-        <v>98.322010000000006</v>
-      </c>
-      <c r="D1096">
-        <v>4.1669855120000001</v>
-      </c>
-    </row>
-    <row r="1097" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1097" s="1">
-        <v>46023</v>
-      </c>
-      <c r="B1097">
-        <v>6845.5</v>
-      </c>
-      <c r="C1097">
-        <v>98.322010000000006</v>
-      </c>
-      <c r="D1097">
-        <v>4.1669855120000001</v>
-      </c>
-    </row>
-    <row r="1098" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1098" s="1">
-        <v>46024</v>
-      </c>
-      <c r="B1098">
-        <v>6858.47</v>
-      </c>
-      <c r="C1098">
-        <v>98.424000000000007</v>
-      </c>
-      <c r="D1098">
-        <v>4.190676689</v>
-      </c>
-    </row>
-    <row r="1099" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1099" s="1">
-        <v>46025</v>
-      </c>
-      <c r="B1099">
-        <v>6858.47</v>
-      </c>
-      <c r="C1099">
-        <v>98.424000000000007</v>
-      </c>
-      <c r="D1099">
-        <v>4.190676689</v>
-      </c>
-    </row>
-    <row r="1100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1100" s="1">
-        <v>46026</v>
-      </c>
-      <c r="B1100">
-        <v>6858.47</v>
-      </c>
-      <c r="C1100">
-        <v>98.424000000000007</v>
-      </c>
-      <c r="D1100">
-        <v>4.190676689</v>
-      </c>
-    </row>
-    <row r="1101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1101" s="1">
-        <v>46027</v>
-      </c>
-      <c r="B1101">
-        <v>6902.05</v>
-      </c>
-      <c r="C1101">
-        <v>98.27</v>
-      </c>
-      <c r="D1101">
-        <v>4.1612205510000004</v>
-      </c>
-    </row>
-    <row r="1102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1102" s="1">
-        <v>46028</v>
-      </c>
-      <c r="B1102">
-        <v>6944.82</v>
-      </c>
-      <c r="C1102">
-        <v>98.58</v>
-      </c>
-      <c r="D1102">
-        <v>4.1730413439999996</v>
-      </c>
-    </row>
-    <row r="1103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1103" s="1">
-        <v>46029</v>
-      </c>
-      <c r="B1103">
-        <v>6920.93</v>
-      </c>
-      <c r="C1103">
-        <v>98.684010000000001</v>
-      </c>
-      <c r="D1103">
-        <v>4.1475400919999998</v>
-      </c>
-    </row>
-    <row r="1104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1104" s="1">
-        <v>46030</v>
-      </c>
-      <c r="B1104">
-        <v>6921.46</v>
-      </c>
-      <c r="C1104">
-        <v>98.934010000000001</v>
-      </c>
-      <c r="D1104">
-        <v>4.1672096249999999</v>
-      </c>
-    </row>
-    <row r="1105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1105" s="1">
-        <v>46031</v>
-      </c>
-      <c r="B1105">
-        <v>6966.28</v>
-      </c>
-      <c r="C1105">
-        <v>99.132999999999996</v>
-      </c>
-      <c r="D1105">
-        <v>4.1653413769999998</v>
-      </c>
-    </row>
-    <row r="1106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1106" s="1">
-        <v>46032</v>
-      </c>
-      <c r="B1106">
-        <v>6966.28</v>
-      </c>
-      <c r="C1106">
-        <v>99.132999999999996</v>
-      </c>
-      <c r="D1106">
-        <v>4.1653413769999998</v>
-      </c>
-    </row>
-    <row r="1107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1107" s="1">
-        <v>46033</v>
-      </c>
-      <c r="B1107">
-        <v>6966.28</v>
-      </c>
-      <c r="C1107">
-        <v>99.132999999999996</v>
-      </c>
-      <c r="D1107">
-        <v>4.1653413769999998</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1108" s="1">
-        <v>46034</v>
-      </c>
-      <c r="B1108">
-        <v>6977.27</v>
-      </c>
-      <c r="C1108">
-        <v>98.862009999999998</v>
-      </c>
-      <c r="D1108">
-        <v>4.1752157209999998</v>
-      </c>
-    </row>
-    <row r="1109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1109" s="1">
-        <v>46035</v>
-      </c>
-      <c r="B1109">
-        <v>6963.74</v>
-      </c>
-      <c r="C1109">
-        <v>99.134</v>
-      </c>
-      <c r="D1109">
-        <v>4.1791915890000002</v>
-      </c>
-    </row>
-    <row r="1110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1110" s="1">
-        <v>46036</v>
-      </c>
-      <c r="B1110">
-        <v>6926.6</v>
-      </c>
-      <c r="C1110">
-        <v>99.055000000000007</v>
-      </c>
-      <c r="D1110">
-        <v>4.1320323940000003</v>
-      </c>
-    </row>
-    <row r="1111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1111" s="1">
-        <v>46037</v>
-      </c>
-      <c r="B1111">
-        <v>6944.47</v>
-      </c>
-      <c r="C1111">
-        <v>99.321010000000001</v>
-      </c>
-      <c r="D1111">
-        <v>4.1694126130000004</v>
-      </c>
-    </row>
-    <row r="1112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1112" s="1">
-        <v>46038</v>
-      </c>
-      <c r="B1112">
-        <v>6940.01</v>
-      </c>
-      <c r="C1112">
-        <v>99.393010000000004</v>
-      </c>
-      <c r="D1112">
-        <v>4.2229099269999999</v>
-      </c>
-    </row>
-    <row r="1113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1113" s="1">
-        <v>46039</v>
-      </c>
-      <c r="B1113">
-        <v>6940.01</v>
-      </c>
-      <c r="C1113">
-        <v>99.393010000000004</v>
-      </c>
-      <c r="D1113">
-        <v>4.2229099269999999</v>
-      </c>
-    </row>
-    <row r="1114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1114" s="1">
-        <v>46040</v>
-      </c>
-      <c r="B1114">
-        <v>6940.01</v>
-      </c>
-      <c r="C1114">
-        <v>99.393010000000004</v>
-      </c>
-      <c r="D1114">
-        <v>4.2229099269999999</v>
-      </c>
-    </row>
-    <row r="1115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1115" s="1">
-        <v>46041</v>
-      </c>
-      <c r="B1115">
-        <v>6940.01</v>
-      </c>
-      <c r="C1115">
-        <v>99.393010000000004</v>
-      </c>
-      <c r="D1115">
-        <v>4.2229099269999999</v>
-      </c>
-    </row>
-    <row r="1116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1116" s="1">
-        <v>46042</v>
-      </c>
-      <c r="B1116">
-        <v>6796.86</v>
-      </c>
-      <c r="C1116">
-        <v>98.641009999999994</v>
-      </c>
-      <c r="D1116">
-        <v>4.2925462720000001</v>
-      </c>
-    </row>
-    <row r="1117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1117" s="1">
-        <v>46043</v>
-      </c>
-      <c r="B1117">
-        <v>6875.62</v>
-      </c>
-      <c r="C1117">
-        <v>98.760999999999996</v>
-      </c>
-      <c r="D1117">
-        <v>4.2428455349999998</v>
-      </c>
-    </row>
-    <row r="1118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1118" s="1">
-        <v>46044</v>
-      </c>
-      <c r="B1118">
-        <v>6913.35</v>
-      </c>
-      <c r="C1118">
-        <v>98.358999999999995</v>
-      </c>
-      <c r="D1118">
-        <v>4.2448835369999998</v>
-      </c>
-    </row>
-    <row r="1119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1119" s="1">
-        <v>46045</v>
-      </c>
-      <c r="B1119">
-        <v>6915.61</v>
-      </c>
-      <c r="C1119">
-        <v>97.599010000000007</v>
-      </c>
-      <c r="D1119">
-        <v>4.2251815800000001</v>
-      </c>
-    </row>
-    <row r="1120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1120" s="1">
-        <v>46046</v>
-      </c>
-      <c r="B1120">
-        <v>6915.61</v>
-      </c>
-      <c r="C1120">
-        <v>97.599010000000007</v>
-      </c>
-      <c r="D1120">
-        <v>4.2251815800000001</v>
-      </c>
-    </row>
-    <row r="1121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1121" s="1">
-        <v>46047</v>
-      </c>
-      <c r="B1121">
-        <v>6915.61</v>
-      </c>
-      <c r="C1121">
-        <v>97.599010000000007</v>
-      </c>
-      <c r="D1121">
-        <v>4.2251815800000001</v>
-      </c>
-    </row>
-    <row r="1122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1122" s="1">
-        <v>46048</v>
-      </c>
-      <c r="B1122">
-        <v>6950.23</v>
-      </c>
-      <c r="C1122">
-        <v>97.04</v>
-      </c>
-      <c r="D1122">
-        <v>4.2113456730000003</v>
-      </c>
-    </row>
-    <row r="1123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1123" s="1">
-        <v>46049</v>
-      </c>
-      <c r="B1123">
-        <v>6978.6</v>
-      </c>
-      <c r="C1123">
-        <v>96.216999999999999</v>
-      </c>
-      <c r="D1123">
-        <v>4.2431621550000003</v>
-      </c>
-    </row>
-    <row r="1124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1124" s="1">
-        <v>46050</v>
-      </c>
-      <c r="B1124">
-        <v>6978.03</v>
-      </c>
-      <c r="C1124">
-        <v>96.446010000000001</v>
-      </c>
-      <c r="D1124">
-        <v>4.2432155610000004</v>
-      </c>
-    </row>
-    <row r="1125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1125" s="1">
-        <v>46051</v>
-      </c>
-      <c r="B1125">
-        <v>6969.01</v>
-      </c>
-      <c r="C1125">
-        <v>96.283000000000001</v>
-      </c>
-      <c r="D1125">
-        <v>4.2313385009999998</v>
-      </c>
-    </row>
-    <row r="1126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1126" s="1">
-        <v>46052</v>
-      </c>
-      <c r="B1126">
-        <v>6939.03</v>
-      </c>
-      <c r="C1126">
-        <v>96.991</v>
-      </c>
-      <c r="D1126">
-        <v>4.2354707720000002</v>
-      </c>
-    </row>
-    <row r="1127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1127" s="1">
-        <v>46053</v>
-      </c>
-      <c r="B1127">
-        <v>6939.03</v>
-      </c>
-      <c r="C1127">
-        <v>96.991</v>
-      </c>
-      <c r="D1127">
-        <v>4.2354707720000002</v>
-      </c>
-    </row>
-    <row r="1128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1128" s="1">
-        <v>46054</v>
-      </c>
-      <c r="B1128">
-        <v>6939.03</v>
-      </c>
-      <c r="C1128">
-        <v>96.991</v>
-      </c>
-      <c r="D1128">
-        <v>4.2354707720000002</v>
-      </c>
-    </row>
-    <row r="1129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1129" s="1">
-        <v>46055</v>
-      </c>
-      <c r="B1129">
-        <v>6976.44</v>
-      </c>
-      <c r="C1129">
-        <v>97.632000000000005</v>
-      </c>
-      <c r="D1129">
-        <v>4.2773923869999999</v>
-      </c>
-    </row>
-    <row r="1130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1130" s="1">
-        <v>46056</v>
-      </c>
-      <c r="B1130">
-        <v>6917.81</v>
-      </c>
-      <c r="C1130">
-        <v>97.436999999999998</v>
-      </c>
-      <c r="D1130">
-        <v>4.2654724120000003</v>
-      </c>
-    </row>
-    <row r="1131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1131" s="1">
-        <v>46057</v>
-      </c>
-      <c r="B1131">
-        <v>6882.72</v>
-      </c>
-      <c r="C1131">
-        <v>97.616</v>
-      </c>
-      <c r="D1131">
-        <v>4.273521423</v>
-      </c>
-    </row>
-    <row r="1132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1132" s="1">
-        <v>46058</v>
-      </c>
-      <c r="B1132">
-        <v>6798.4</v>
-      </c>
-      <c r="C1132">
-        <v>97.824010000000001</v>
-      </c>
-      <c r="D1132">
-        <v>4.180072784</v>
-      </c>
-    </row>
-    <row r="1133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1133" s="1">
-        <v>46059</v>
-      </c>
-      <c r="B1133">
-        <v>6932.3</v>
-      </c>
-      <c r="C1133">
-        <v>97.632999999999996</v>
-      </c>
-      <c r="D1133">
-        <v>4.2059955599999999</v>
-      </c>
-    </row>
-    <row r="1134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1134" s="1">
-        <v>46060</v>
-      </c>
-      <c r="B1134">
-        <v>6932.3</v>
-      </c>
-      <c r="C1134">
-        <v>97.632999999999996</v>
-      </c>
-      <c r="D1134">
-        <v>4.2059955599999999</v>
-      </c>
-    </row>
-    <row r="1135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1135" s="1">
-        <v>46061</v>
-      </c>
-      <c r="B1135">
-        <v>6932.3</v>
-      </c>
-      <c r="C1135">
-        <v>97.632999999999996</v>
-      </c>
-      <c r="D1135">
-        <v>4.2059955599999999</v>
-      </c>
-    </row>
-    <row r="1136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1136" s="1">
-        <v>46062</v>
-      </c>
-      <c r="B1136">
-        <v>6964.82</v>
-      </c>
-      <c r="C1136">
-        <v>96.816000000000003</v>
-      </c>
-      <c r="D1136">
-        <v>4.2020683290000003</v>
-      </c>
-    </row>
-    <row r="1137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1137" s="1">
-        <v>46063</v>
-      </c>
-      <c r="B1137">
-        <v>6941.81</v>
-      </c>
-      <c r="C1137">
-        <v>96.799000000000007</v>
-      </c>
-      <c r="D1137">
-        <v>4.1426649089999996</v>
-      </c>
-    </row>
-    <row r="1138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1138" s="1">
-        <v>46064</v>
-      </c>
-      <c r="B1138">
-        <v>6941.47</v>
-      </c>
-      <c r="C1138">
-        <v>96.834010000000006</v>
-      </c>
-      <c r="D1138">
-        <v>4.1723880769999999</v>
-      </c>
-    </row>
-    <row r="1139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1139" s="1">
-        <v>46065</v>
-      </c>
-      <c r="B1139">
-        <v>6832.76</v>
-      </c>
-      <c r="C1139">
-        <v>96.924999999999997</v>
-      </c>
-      <c r="D1139">
-        <v>4.0980777740000001</v>
-      </c>
-    </row>
-    <row r="1140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1140" s="1">
-        <v>46066</v>
-      </c>
-      <c r="B1140">
-        <v>6836.17</v>
-      </c>
-      <c r="C1140">
-        <v>96.915000000000006</v>
-      </c>
-      <c r="D1140">
-        <v>4.0483140950000003</v>
-      </c>
-    </row>
-    <row r="1141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1141" s="1">
-        <v>46067</v>
-      </c>
-      <c r="B1141">
-        <v>6836.17</v>
-      </c>
-      <c r="C1141">
-        <v>96.915000000000006</v>
-      </c>
-      <c r="D1141">
-        <v>4.0483140950000003</v>
-      </c>
-    </row>
-    <row r="1142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1142" s="1">
-        <v>46068</v>
-      </c>
-      <c r="B1142">
-        <v>6836.17</v>
-      </c>
-      <c r="C1142">
-        <v>96.915000000000006</v>
-      </c>
-      <c r="D1142">
-        <v>4.0483140950000003</v>
-      </c>
-    </row>
-    <row r="1143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1143" s="1">
-        <v>46069</v>
-      </c>
-      <c r="B1143">
-        <v>6836.17</v>
-      </c>
-      <c r="C1143">
-        <v>96.915000000000006</v>
-      </c>
-      <c r="D1143">
-        <v>4.0483140950000003</v>
-      </c>
-    </row>
-    <row r="1144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1144" s="1">
-        <v>46070</v>
-      </c>
-      <c r="B1144">
-        <v>6843.22</v>
-      </c>
-      <c r="C1144">
-        <v>97.155010000000004</v>
-      </c>
-      <c r="D1144">
-        <v>4.0578365329999997</v>
-      </c>
-    </row>
-    <row r="1145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1145" s="1">
-        <v>46071</v>
-      </c>
-      <c r="B1145">
-        <v>6881.31</v>
-      </c>
-      <c r="C1145">
-        <v>97.703000000000003</v>
-      </c>
-      <c r="D1145">
-        <v>4.0826940540000001</v>
-      </c>
-    </row>
-    <row r="1146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1146" s="1">
-        <v>46072</v>
-      </c>
-      <c r="B1146">
-        <v>6861.89</v>
-      </c>
-      <c r="C1146">
-        <v>97.924999999999997</v>
-      </c>
-      <c r="D1146">
-        <v>4.067346573</v>
-      </c>
-    </row>
-    <row r="1147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1147" s="1">
-        <v>46073</v>
-      </c>
-      <c r="B1147">
-        <v>6909.51</v>
-      </c>
-      <c r="C1147">
-        <v>97.796009999999995</v>
-      </c>
-      <c r="D1147">
-        <v>4.0826034550000001</v>
-      </c>
-    </row>
-    <row r="1148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1148" s="1">
-        <v>46074</v>
-      </c>
-      <c r="B1148">
-        <v>6909.51</v>
-      </c>
-      <c r="C1148">
-        <v>97.796009999999995</v>
-      </c>
-      <c r="D1148">
-        <v>4.0826034550000001</v>
-      </c>
-    </row>
-    <row r="1149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1149" s="1">
-        <v>46075</v>
-      </c>
-      <c r="B1149">
-        <v>6909.51</v>
-      </c>
-      <c r="C1149">
-        <v>97.796009999999995</v>
-      </c>
-      <c r="D1149">
-        <v>4.0826034550000001</v>
-      </c>
-    </row>
-    <row r="1150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1150" s="1">
-        <v>46076</v>
-      </c>
-      <c r="B1150">
-        <v>6837.75</v>
-      </c>
-      <c r="C1150">
-        <v>97.706000000000003</v>
-      </c>
-      <c r="D1150">
-        <v>4.0309047700000002</v>
-      </c>
-    </row>
-    <row r="1151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1151" s="1">
-        <v>46077</v>
-      </c>
-      <c r="B1151">
-        <v>6890.07</v>
-      </c>
-      <c r="C1151">
-        <v>97.843000000000004</v>
-      </c>
-      <c r="D1151">
-        <v>4.0289621350000004</v>
-      </c>
-    </row>
-    <row r="1152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1152" s="1">
-        <v>46078</v>
-      </c>
-      <c r="B1152">
-        <v>6946.13</v>
-      </c>
-      <c r="C1152">
-        <v>97.7</v>
-      </c>
-      <c r="D1152">
-        <v>4.0518693920000004</v>
-      </c>
-    </row>
-    <row r="1153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1153" s="1">
-        <v>46079</v>
-      </c>
-      <c r="B1153">
-        <v>6908.86</v>
-      </c>
-      <c r="C1153">
-        <v>97.79101</v>
-      </c>
-      <c r="D1153">
-        <v>4.00409317</v>
-      </c>
-    </row>
-    <row r="1154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1154" s="1">
-        <v>46080</v>
-      </c>
-      <c r="B1154">
-        <v>6878.88</v>
-      </c>
-      <c r="C1154">
-        <v>97.608000000000004</v>
-      </c>
-      <c r="D1154">
-        <v>3.9374504090000002</v>
-      </c>
-    </row>
-    <row r="1155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1155" s="1">
-        <v>46081</v>
-      </c>
-      <c r="B1155">
-        <v>6878.88</v>
-      </c>
-      <c r="C1155">
-        <v>97.608000000000004</v>
-      </c>
-      <c r="D1155">
-        <v>3.9374504090000002</v>
-      </c>
-    </row>
-    <row r="1156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1156" s="1">
-        <v>46082</v>
-      </c>
-      <c r="B1156">
-        <v>6878.88</v>
-      </c>
-      <c r="C1156">
-        <v>97.608000000000004</v>
-      </c>
-      <c r="D1156">
-        <v>3.9374504090000002</v>
-      </c>
-    </row>
-    <row r="1157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1157" s="1">
-        <v>46083</v>
-      </c>
-      <c r="B1157">
-        <v>6881.62</v>
-      </c>
-      <c r="C1157">
-        <v>98.381</v>
-      </c>
-      <c r="D1157">
-        <v>4.0344982150000002</v>
-      </c>
-    </row>
-    <row r="1158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1158" s="1">
-        <v>46084</v>
-      </c>
-      <c r="B1158">
-        <v>6816.63</v>
-      </c>
-      <c r="C1158">
-        <v>99.052000000000007</v>
-      </c>
-      <c r="D1158">
-        <v>4.0593681339999996</v>
-      </c>
-    </row>
-    <row r="1159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1159" s="1">
-        <v>46085</v>
-      </c>
-      <c r="B1159">
-        <v>6869.5</v>
-      </c>
-      <c r="C1159">
-        <v>98.769000000000005</v>
-      </c>
-      <c r="D1159">
-        <v>4.0958528520000002</v>
-      </c>
-    </row>
-    <row r="1160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1160" s="1">
-        <v>46086</v>
-      </c>
-      <c r="B1160">
-        <v>6830.71</v>
-      </c>
-      <c r="C1160">
-        <v>99.316999999999993</v>
-      </c>
-      <c r="D1160">
-        <v>4.1363477709999996</v>
-      </c>
-    </row>
-    <row r="1161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1161" s="1">
-        <v>46087</v>
-      </c>
-      <c r="B1161">
-        <v>6740.02</v>
-      </c>
-      <c r="C1161">
-        <v>98.986009999999993</v>
-      </c>
-      <c r="D1161">
-        <v>4.138256073</v>
-      </c>
-    </row>
-    <row r="1162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1162" s="1">
-        <v>46088</v>
-      </c>
-      <c r="B1162">
-        <v>6740.02</v>
-      </c>
-      <c r="C1162">
-        <v>98.986009999999993</v>
-      </c>
-      <c r="D1162">
-        <v>4.138256073</v>
-      </c>
-    </row>
-    <row r="1163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1163" s="1">
-        <v>46089</v>
-      </c>
-      <c r="B1163">
-        <v>6740.02</v>
-      </c>
-      <c r="C1163">
-        <v>98.986009999999993</v>
-      </c>
-      <c r="D1163">
-        <v>4.138256073</v>
-      </c>
-    </row>
-    <row r="1164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1164" s="1">
-        <v>46090</v>
-      </c>
-      <c r="B1164">
-        <v>6795.99</v>
-      </c>
-      <c r="C1164">
-        <v>99.174999999999997</v>
-      </c>
-      <c r="D1164">
-        <v>4.0957651139999998</v>
-      </c>
-    </row>
-    <row r="1165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1165" s="1">
-        <v>46091</v>
-      </c>
-      <c r="B1165">
-        <v>6781.48</v>
-      </c>
-      <c r="C1165">
-        <v>98.825999999999993</v>
-      </c>
-      <c r="D1165">
-        <v>4.1556739809999996</v>
-      </c>
-    </row>
-    <row r="1166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1166" s="1">
-        <v>46092</v>
-      </c>
-      <c r="B1166">
-        <v>6775.8</v>
-      </c>
-      <c r="C1166">
-        <v>99.230999999999995</v>
-      </c>
-      <c r="D1166">
-        <v>4.2296152109999996</v>
-      </c>
-    </row>
-    <row r="1167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1167" s="1">
-        <v>46093</v>
-      </c>
-      <c r="B1167">
-        <v>6672.62</v>
-      </c>
-      <c r="C1167">
-        <v>99.739009999999993</v>
-      </c>
-      <c r="D1167">
-        <v>4.2609262469999996</v>
-      </c>
-    </row>
-    <row r="1168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1168" s="1">
-        <v>46094</v>
-      </c>
-      <c r="B1168">
-        <v>6632.19</v>
-      </c>
-      <c r="C1168">
-        <v>100.36199999999999</v>
-      </c>
-      <c r="D1168">
-        <v>4.2766818999999998</v>
-      </c>
-    </row>
-    <row r="1169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1169" s="1">
-        <v>46095</v>
-      </c>
-      <c r="B1169">
-        <v>6632.19</v>
-      </c>
-      <c r="C1169">
-        <v>100.36199999999999</v>
-      </c>
-      <c r="D1169">
-        <v>4.2766818999999998</v>
-      </c>
-    </row>
-    <row r="1170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1170" s="1">
-        <v>46096</v>
-      </c>
-      <c r="B1170">
-        <v>6632.19</v>
-      </c>
-      <c r="C1170">
-        <v>100.36199999999999</v>
-      </c>
-      <c r="D1170">
-        <v>4.2766818999999998</v>
-      </c>
-    </row>
-    <row r="1171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1171" s="1">
-        <v>46097</v>
-      </c>
-      <c r="B1171">
-        <v>6699.38</v>
-      </c>
-      <c r="C1171">
-        <v>99.712010000000006</v>
-      </c>
-      <c r="D1171">
-        <v>4.2160053250000002</v>
-      </c>
-    </row>
-    <row r="1172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1172" s="1">
-        <v>46098</v>
-      </c>
-      <c r="B1172">
-        <v>6716.09</v>
-      </c>
-      <c r="C1172">
-        <v>99.575000000000003</v>
-      </c>
-      <c r="D1172">
-        <v>4.1984548569999998</v>
-      </c>
-    </row>
-    <row r="1173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1173" s="1">
-        <v>46099</v>
-      </c>
-      <c r="B1173">
-        <v>6624.7</v>
-      </c>
-      <c r="C1173">
-        <v>100.086</v>
-      </c>
-      <c r="D1173">
-        <v>4.26497364</v>
-      </c>
-    </row>
-    <row r="1174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1174" s="1">
-        <v>46100</v>
-      </c>
-      <c r="B1174">
-        <v>6606.49</v>
-      </c>
-      <c r="C1174">
-        <v>99.231999999999999</v>
-      </c>
-      <c r="D1174">
-        <v>4.2493038179999996</v>
-      </c>
-    </row>
-    <row r="1175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1175" s="1">
-        <v>46101</v>
-      </c>
-      <c r="B1175">
-        <v>6506.48</v>
-      </c>
-      <c r="C1175">
-        <v>99.647000000000006</v>
-      </c>
-      <c r="D1175">
-        <v>4.3796081539999996</v>
-      </c>
-    </row>
-    <row r="1176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1176" s="1">
-        <v>46102</v>
-      </c>
-      <c r="B1176">
-        <v>6506.48</v>
-      </c>
-      <c r="C1176">
-        <v>99.647000000000006</v>
-      </c>
-      <c r="D1176">
-        <v>4.3796081539999996</v>
-      </c>
-    </row>
-    <row r="1177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1177" s="1">
-        <v>46103</v>
-      </c>
-      <c r="B1177">
-        <v>6506.48</v>
-      </c>
-      <c r="C1177">
-        <v>99.647000000000006</v>
-      </c>
-      <c r="D1177">
-        <v>4.3796081539999996</v>
-      </c>
-    </row>
-    <row r="1178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1178" s="1">
-        <v>46104</v>
-      </c>
-      <c r="B1178">
-        <v>6581</v>
-      </c>
-      <c r="C1178">
-        <v>98.95</v>
-      </c>
-      <c r="D1178">
-        <v>4.3419866560000004</v>
-      </c>
-    </row>
-    <row r="1179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1179" s="1">
-        <v>46105</v>
-      </c>
-      <c r="B1179">
-        <v>6556.37</v>
-      </c>
-      <c r="C1179">
-        <v>99.434010000000001</v>
-      </c>
-      <c r="D1179">
-        <v>4.3598575589999999</v>
-      </c>
-    </row>
-    <row r="1180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1180" s="1">
-        <v>46106</v>
-      </c>
-      <c r="B1180">
-        <v>6591.9</v>
-      </c>
-      <c r="C1180">
-        <v>99.599010000000007</v>
-      </c>
-      <c r="D1180">
-        <v>4.3321714399999998</v>
-      </c>
-    </row>
-    <row r="1181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1181" s="1">
-        <v>46107</v>
-      </c>
-      <c r="B1181">
-        <v>6477.16</v>
-      </c>
-      <c r="C1181">
-        <v>99.9</v>
-      </c>
-      <c r="D1181">
-        <v>4.4116506580000001</v>
-      </c>
-    </row>
-    <row r="1182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1182" s="1">
-        <v>46108</v>
-      </c>
-      <c r="B1182">
-        <v>6368.85</v>
-      </c>
-      <c r="C1182">
-        <v>100.151</v>
-      </c>
-      <c r="D1182">
-        <v>4.4277915950000004</v>
-      </c>
-    </row>
-    <row r="1183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1183" s="1">
-        <v>46109</v>
-      </c>
-      <c r="B1183">
-        <v>6368.85</v>
-      </c>
-      <c r="C1183">
-        <v>100.151</v>
-      </c>
-      <c r="D1183">
-        <v>4.4277915950000004</v>
-      </c>
-    </row>
-    <row r="1184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1184" s="1">
-        <v>46110</v>
-      </c>
-      <c r="B1184">
-        <v>6368.85</v>
-      </c>
-      <c r="C1184">
-        <v>100.151</v>
-      </c>
-      <c r="D1184">
-        <v>4.4277915950000004</v>
-      </c>
-    </row>
-    <row r="1185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1185" s="1">
-        <v>46111</v>
-      </c>
-      <c r="B1185">
-        <v>6343.72</v>
-      </c>
-      <c r="C1185">
-        <v>100.509</v>
-      </c>
-      <c r="D1185">
-        <v>4.3482189179999997</v>
-      </c>
-    </row>
-    <row r="1186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1186" s="1">
-        <v>46112</v>
-      </c>
-      <c r="B1186">
-        <v>6528.52</v>
-      </c>
-      <c r="C1186">
-        <v>99.961010000000002</v>
-      </c>
-      <c r="D1186">
-        <v>4.3165702819999998</v>
-      </c>
-    </row>
-    <row r="1187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1187" s="1">
-        <v>46113</v>
-      </c>
-      <c r="B1187">
-        <v>6575.32</v>
-      </c>
-      <c r="C1187">
-        <v>99.650999999999996</v>
-      </c>
-      <c r="D1187">
-        <v>4.3185844419999997</v>
-      </c>
-    </row>
-    <row r="1188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1188" s="1">
-        <v>46114</v>
-      </c>
-      <c r="B1188">
-        <v>6582.69</v>
-      </c>
-      <c r="C1188">
-        <v>100.02800000000001</v>
-      </c>
-      <c r="D1188">
-        <v>4.3048772810000004</v>
-      </c>
-    </row>
-    <row r="1189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1189" s="1">
-        <v>46115</v>
-      </c>
-      <c r="B1189">
-        <v>6582.69</v>
-      </c>
-      <c r="C1189">
-        <v>100.02800000000001</v>
-      </c>
-      <c r="D1189">
-        <v>4.3405799869999999</v>
-      </c>
-    </row>
-    <row r="1190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1190" s="1">
-        <v>46116</v>
-      </c>
-      <c r="B1190">
-        <v>6582.69</v>
-      </c>
-      <c r="C1190">
-        <v>100.02800000000001</v>
-      </c>
-      <c r="D1190">
-        <v>4.3405799869999999</v>
-      </c>
-    </row>
-    <row r="1191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1191" s="1">
-        <v>46117</v>
-      </c>
-      <c r="B1191">
-        <v>6582.69</v>
-      </c>
-      <c r="C1191">
-        <v>100.02800000000001</v>
-      </c>
-      <c r="D1191">
-        <v>4.3405799869999999</v>
-      </c>
-    </row>
-    <row r="1192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1192" s="1">
-        <v>46118</v>
-      </c>
-      <c r="B1192">
-        <v>6611.83</v>
-      </c>
-      <c r="C1192">
-        <v>99.980999999999995</v>
-      </c>
-      <c r="D1192">
-        <v>4.3306598660000004</v>
-      </c>
-    </row>
-    <row r="1193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1193" s="1">
-        <v>46119</v>
-      </c>
-      <c r="B1193">
-        <v>6616.85</v>
-      </c>
-      <c r="C1193">
-        <v>99.858000000000004</v>
-      </c>
-      <c r="D1193">
-        <v>4.2930803299999996</v>
-      </c>
-    </row>
-    <row r="1194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1194" s="1">
-        <v>46120</v>
-      </c>
-      <c r="B1194">
-        <v>6782.81</v>
-      </c>
-      <c r="C1194">
-        <v>99.132999999999996</v>
-      </c>
-      <c r="D1194">
-        <v>4.2911357880000001</v>
-      </c>
-    </row>
-    <row r="1195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1195" s="1">
-        <v>46121</v>
-      </c>
-      <c r="B1195">
-        <v>6824.66</v>
-      </c>
-      <c r="C1195">
-        <v>98.819010000000006</v>
-      </c>
-      <c r="D1195">
-        <v>4.2753639220000004</v>
-      </c>
-    </row>
-    <row r="1196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1196" s="1">
-        <v>46122</v>
-      </c>
-      <c r="B1196">
-        <v>6816.89</v>
-      </c>
-      <c r="C1196">
-        <v>98.65</v>
-      </c>
-      <c r="D1196">
-        <v>4.3170118329999996</v>
-      </c>
-    </row>
-    <row r="1197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1197" s="1">
-        <v>46123</v>
-      </c>
-      <c r="B1197">
-        <v>6816.89</v>
-      </c>
-      <c r="C1197">
-        <v>98.65</v>
-      </c>
-      <c r="D1197">
-        <v>4.3170118329999996</v>
-      </c>
-    </row>
-    <row r="1198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1198" s="1">
-        <v>46124</v>
-      </c>
-      <c r="B1198">
-        <v>6816.89</v>
-      </c>
-      <c r="C1198">
-        <v>98.65</v>
-      </c>
-      <c r="D1198">
-        <v>4.3170118329999996</v>
-      </c>
-    </row>
-    <row r="1199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1199" s="1">
-        <v>46125</v>
-      </c>
-      <c r="B1199">
-        <v>6886.24</v>
-      </c>
-      <c r="C1199">
-        <v>98.366</v>
-      </c>
-      <c r="D1199">
-        <v>4.2932739260000004</v>
-      </c>
-    </row>
-    <row r="1200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1200" s="1">
-        <v>46126</v>
-      </c>
-      <c r="B1200">
-        <v>6967.38</v>
-      </c>
-      <c r="C1200">
-        <v>98.124009999999998</v>
-      </c>
-      <c r="D1200">
-        <v>4.2478752139999996</v>
-      </c>
-    </row>
-    <row r="1201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1201" s="1">
-        <v>46127</v>
-      </c>
-      <c r="B1201">
-        <v>7022.95</v>
-      </c>
-      <c r="C1201">
-        <v>98.055009999999996</v>
-      </c>
-      <c r="D1201">
-        <v>4.2834453579999998</v>
-      </c>
-    </row>
-    <row r="1202" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1202" s="1">
-        <v>46128</v>
-      </c>
-      <c r="B1202">
-        <v>7041.28</v>
-      </c>
-      <c r="C1202">
-        <v>98.215000000000003</v>
-      </c>
-      <c r="D1202">
-        <v>4.3112125399999996</v>
-      </c>
-    </row>
-    <row r="1203" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1203" s="1">
-        <v>46129</v>
-      </c>
-      <c r="B1203">
-        <v>7126.06</v>
-      </c>
-      <c r="C1203">
-        <v>98.098010000000002</v>
-      </c>
-      <c r="D1203">
-        <v>4.2479915620000002</v>
-      </c>
-    </row>
-    <row r="1204" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1204" s="1">
-        <v>46130</v>
-      </c>
-      <c r="B1204">
-        <v>7126.06</v>
-      </c>
-      <c r="C1204">
-        <v>98.098010000000002</v>
-      </c>
-      <c r="D1204">
-        <v>4.2479915620000002</v>
-      </c>
-    </row>
-    <row r="1205" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1205" s="1">
-        <v>46131</v>
-      </c>
-      <c r="B1205">
-        <v>7126.06</v>
-      </c>
-      <c r="C1205">
-        <v>98.098010000000002</v>
-      </c>
-      <c r="D1205">
-        <v>4.2479915620000002</v>
-      </c>
-    </row>
-    <row r="1206" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1206" s="1">
-        <v>46132</v>
-      </c>
-      <c r="B1206">
-        <v>7109.14</v>
-      </c>
-      <c r="C1206">
-        <v>98.097009999999997</v>
-      </c>
-      <c r="D1206">
-        <v>4.2509756090000002</v>
-      </c>
-    </row>
-    <row r="1207" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1207" s="1">
-        <v>46133</v>
-      </c>
-      <c r="B1207">
-        <v>7064.01</v>
-      </c>
-      <c r="C1207">
-        <v>98.394000000000005</v>
-      </c>
-      <c r="D1207">
-        <v>4.2915601729999997</v>
-      </c>
-    </row>
-    <row r="1208" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1208" s="1">
-        <v>46134</v>
-      </c>
-      <c r="B1208">
-        <v>7137.9</v>
-      </c>
-      <c r="C1208">
-        <v>98.59</v>
-      </c>
-      <c r="D1208">
-        <v>4.302505493</v>
-      </c>
-    </row>
-    <row r="1209" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1209" s="1">
-        <v>46135</v>
-      </c>
-      <c r="B1209">
-        <v>7108.4</v>
-      </c>
-      <c r="C1209">
-        <v>98.77</v>
-      </c>
-      <c r="D1209">
-        <v>4.3244028090000004</v>
-      </c>
-    </row>
-    <row r="1210" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1210" s="1">
-        <v>46136</v>
-      </c>
-      <c r="B1210">
-        <v>7165.08</v>
-      </c>
-      <c r="C1210">
-        <v>98.533000000000001</v>
-      </c>
-      <c r="D1210">
-        <v>4.300666809</v>
-      </c>
-    </row>
-    <row r="1211" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1211" s="1">
-        <v>46137</v>
-      </c>
-      <c r="B1211">
-        <v>7165.08</v>
-      </c>
-      <c r="C1211">
-        <v>98.533000000000001</v>
-      </c>
-      <c r="D1211">
-        <v>4.300666809</v>
-      </c>
-    </row>
-    <row r="1212" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1212" s="1">
-        <v>46138</v>
-      </c>
-      <c r="B1212">
-        <v>7165.08</v>
-      </c>
-      <c r="C1212">
-        <v>98.533000000000001</v>
-      </c>
-      <c r="D1212">
-        <v>4.300666809</v>
-      </c>
-    </row>
-    <row r="1213" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1213" s="1">
-        <v>46139</v>
-      </c>
-      <c r="B1213">
-        <v>7173.91</v>
-      </c>
-      <c r="C1213">
-        <v>98.495999999999995</v>
-      </c>
-      <c r="D1213">
-        <v>4.3395156860000004</v>
-      </c>
-    </row>
-    <row r="1214" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1214" s="1">
-        <v>46140</v>
-      </c>
-      <c r="B1214">
-        <v>7138.8</v>
-      </c>
-      <c r="C1214">
-        <v>98.640010000000004</v>
-      </c>
-      <c r="D1214">
-        <v>4.3455467219999999</v>
-      </c>
-    </row>
-    <row r="1215" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1215" s="1">
-        <v>46141</v>
-      </c>
-      <c r="B1215">
-        <v>7135.95</v>
-      </c>
-      <c r="C1215">
-        <v>98.961010000000002</v>
-      </c>
-      <c r="D1215">
-        <v>4.4297609329999998</v>
-      </c>
-    </row>
-    <row r="1216" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1216" s="1">
-        <v>46142</v>
-      </c>
-      <c r="B1216">
-        <v>7209.01</v>
-      </c>
-      <c r="C1216">
-        <v>98.056010000000001</v>
-      </c>
-      <c r="D1216">
-        <v>4.3706274030000003</v>
-      </c>
-    </row>
-    <row r="1217" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1217" s="1">
-        <v>46143</v>
-      </c>
-      <c r="B1217">
-        <v>7230.12</v>
-      </c>
-      <c r="C1217">
-        <v>98.156009999999995</v>
-      </c>
-      <c r="D1217">
-        <v>4.3697881699999996</v>
-      </c>
-    </row>
-    <row r="1218" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1218" s="1">
-        <v>46144</v>
-      </c>
-      <c r="B1218">
-        <v>7230.12</v>
-      </c>
-      <c r="C1218">
-        <v>98.156009999999995</v>
-      </c>
-      <c r="D1218">
-        <v>4.3697881699999996</v>
-      </c>
-    </row>
-    <row r="1219" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1219" s="1">
-        <v>46145</v>
-      </c>
-      <c r="B1219">
-        <v>7230.12</v>
-      </c>
-      <c r="C1219">
-        <v>98.156009999999995</v>
-      </c>
-      <c r="D1219">
-        <v>4.3697881699999996</v>
-      </c>
-    </row>
-    <row r="1220" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1220" s="1">
-        <v>46146</v>
-      </c>
-      <c r="B1220">
-        <v>7200.75</v>
-      </c>
-      <c r="C1220">
-        <v>98.374009999999998</v>
-      </c>
-      <c r="D1220">
-        <v>4.4381580349999998</v>
-      </c>
-    </row>
-    <row r="1221" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1221" s="1">
-        <v>46147</v>
-      </c>
-      <c r="B1221">
-        <v>7259.22</v>
-      </c>
-      <c r="C1221">
-        <v>98.444010000000006</v>
-      </c>
-      <c r="D1221">
-        <v>4.424123764</v>
-      </c>
-    </row>
-    <row r="1222" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1222" s="1">
-        <v>46148</v>
-      </c>
-      <c r="B1222">
-        <v>7365.12</v>
-      </c>
-      <c r="C1222">
-        <v>98.022999999999996</v>
-      </c>
-      <c r="D1222">
-        <v>4.3489322660000003</v>
-      </c>
-    </row>
-    <row r="1223" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1223" s="1">
-        <v>46149</v>
-      </c>
-      <c r="B1223">
-        <v>7337.11</v>
-      </c>
-      <c r="C1223">
-        <v>98.066999999999993</v>
-      </c>
-      <c r="D1223">
-        <v>4.3860511779999998</v>
-      </c>
-    </row>
-    <row r="1224" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1224" s="1">
-        <v>46150</v>
-      </c>
-      <c r="B1224">
-        <v>7398.93</v>
-      </c>
-      <c r="C1224">
-        <v>97.9</v>
-      </c>
-      <c r="D1224">
-        <v>4.3541374209999999</v>
-      </c>
-    </row>
-    <row r="1225" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1225" s="1">
-        <v>46151</v>
-      </c>
-      <c r="B1225">
-        <v>7398.93</v>
-      </c>
-      <c r="C1225">
-        <v>97.9</v>
-      </c>
-      <c r="D1225">
-        <v>4.3541374209999999</v>
-      </c>
-    </row>
-    <row r="1226" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1226" s="1">
-        <v>46152</v>
-      </c>
-      <c r="B1226">
-        <v>7398.93</v>
-      </c>
-      <c r="C1226">
-        <v>97.9</v>
-      </c>
-      <c r="D1226">
-        <v>4.3541374209999999</v>
-      </c>
-    </row>
-    <row r="1227" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1227" s="1">
-        <v>46153</v>
-      </c>
-      <c r="B1227">
-        <v>7398.93</v>
-      </c>
-      <c r="C1227">
-        <v>98.013999938964844</v>
-      </c>
-      <c r="D1227">
-        <v>4.3892402648925781</v>
-      </c>
+      <c r="A896" s="1"/>
+    </row>
+    <row r="897" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A897" s="1"/>
+    </row>
+    <row r="898" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A898" s="1"/>
+    </row>
+    <row r="899" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A899" s="1"/>
+    </row>
+    <row r="900" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A900" s="1"/>
+    </row>
+    <row r="901" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A901" s="1"/>
+    </row>
+    <row r="902" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A902" s="1"/>
+    </row>
+    <row r="903" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A903" s="1"/>
+    </row>
+    <row r="904" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A904" s="1"/>
+    </row>
+    <row r="905" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A905" s="1"/>
+    </row>
+    <row r="906" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A906" s="1"/>
+    </row>
+    <row r="907" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A907" s="1"/>
+    </row>
+    <row r="908" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A908" s="1"/>
+    </row>
+    <row r="909" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A909" s="1"/>
+    </row>
+    <row r="910" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A910" s="1"/>
+    </row>
+    <row r="911" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A911" s="1"/>
+    </row>
+    <row r="912" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A912" s="1"/>
+    </row>
+    <row r="913" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A913" s="1"/>
+    </row>
+    <row r="914" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A914" s="1"/>
+    </row>
+    <row r="915" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A915" s="1"/>
+    </row>
+    <row r="916" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A916" s="1"/>
+    </row>
+    <row r="917" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A917" s="1"/>
+    </row>
+    <row r="918" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A918" s="1"/>
+    </row>
+    <row r="919" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A919" s="1"/>
+    </row>
+    <row r="920" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A920" s="1"/>
+    </row>
+    <row r="921" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A921" s="1"/>
+    </row>
+    <row r="922" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A922" s="1"/>
+    </row>
+    <row r="923" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A923" s="1"/>
+    </row>
+    <row r="924" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A924" s="1"/>
+    </row>
+    <row r="925" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A925" s="1"/>
+    </row>
+    <row r="926" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A926" s="1"/>
+    </row>
+    <row r="927" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A927" s="1"/>
+    </row>
+    <row r="928" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A928" s="1"/>
+    </row>
+    <row r="929" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A929" s="1"/>
+    </row>
+    <row r="930" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A930" s="1"/>
+    </row>
+    <row r="931" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A931" s="1"/>
+    </row>
+    <row r="932" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A932" s="1"/>
+    </row>
+    <row r="933" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A933" s="1"/>
+    </row>
+    <row r="934" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A934" s="1"/>
+    </row>
+    <row r="935" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A935" s="1"/>
+    </row>
+    <row r="936" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A936" s="1"/>
+    </row>
+    <row r="937" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A937" s="1"/>
+    </row>
+    <row r="938" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A938" s="1"/>
+    </row>
+    <row r="939" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A939" s="1"/>
+    </row>
+    <row r="940" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A940" s="1"/>
+    </row>
+    <row r="941" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A941" s="1"/>
+    </row>
+    <row r="942" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A942" s="1"/>
+    </row>
+    <row r="943" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A943" s="1"/>
+    </row>
+    <row r="944" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A944" s="1"/>
+    </row>
+    <row r="945" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A945" s="1"/>
+    </row>
+    <row r="946" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A946" s="1"/>
+    </row>
+    <row r="947" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A947" s="1"/>
+    </row>
+    <row r="948" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A948" s="1"/>
+    </row>
+    <row r="949" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A949" s="1"/>
+    </row>
+    <row r="950" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A950" s="1"/>
+    </row>
+    <row r="951" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A951" s="1"/>
+    </row>
+    <row r="952" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A952" s="1"/>
+    </row>
+    <row r="953" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A953" s="1"/>
+    </row>
+    <row r="954" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A954" s="1"/>
+    </row>
+    <row r="955" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A955" s="1"/>
+    </row>
+    <row r="956" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A956" s="1"/>
+    </row>
+    <row r="957" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A957" s="1"/>
+    </row>
+    <row r="958" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A958" s="1"/>
+    </row>
+    <row r="959" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A959" s="1"/>
+    </row>
+    <row r="960" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A960" s="1"/>
+    </row>
+    <row r="961" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A961" s="1"/>
+    </row>
+    <row r="962" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A962" s="1"/>
+    </row>
+    <row r="963" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A963" s="1"/>
+    </row>
+    <row r="964" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A964" s="1"/>
+    </row>
+    <row r="965" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A965" s="1"/>
+    </row>
+    <row r="966" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A966" s="1"/>
+    </row>
+    <row r="967" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A967" s="1"/>
+    </row>
+    <row r="968" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A968" s="1"/>
+    </row>
+    <row r="969" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A969" s="1"/>
+    </row>
+    <row r="970" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A970" s="1"/>
+    </row>
+    <row r="971" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A971" s="1"/>
+    </row>
+    <row r="972" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A972" s="1"/>
+    </row>
+    <row r="973" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A973" s="1"/>
+    </row>
+    <row r="974" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A974" s="1"/>
+    </row>
+    <row r="975" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A975" s="1"/>
+    </row>
+    <row r="976" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A976" s="1"/>
+    </row>
+    <row r="977" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A977" s="1"/>
+    </row>
+    <row r="978" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A978" s="1"/>
+    </row>
+    <row r="979" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A979" s="1"/>
+    </row>
+    <row r="980" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A980" s="1"/>
+    </row>
+    <row r="981" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A981" s="1"/>
+    </row>
+    <row r="982" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A982" s="1"/>
+    </row>
+    <row r="983" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A983" s="1"/>
+    </row>
+    <row r="984" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A984" s="1"/>
+    </row>
+    <row r="985" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A985" s="1"/>
+    </row>
+    <row r="986" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A986" s="1"/>
+    </row>
+    <row r="987" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A987" s="1"/>
+    </row>
+    <row r="988" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A988" s="1"/>
+    </row>
+    <row r="989" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A989" s="1"/>
+    </row>
+    <row r="990" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A990" s="1"/>
+    </row>
+    <row r="991" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A991" s="1"/>
+    </row>
+    <row r="992" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A992" s="1"/>
+    </row>
+    <row r="993" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A993" s="1"/>
+    </row>
+    <row r="994" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A994" s="1"/>
+    </row>
+    <row r="995" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A995" s="1"/>
+    </row>
+    <row r="996" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A996" s="1"/>
+    </row>
+    <row r="997" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A997" s="1"/>
+    </row>
+    <row r="998" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A998" s="1"/>
+    </row>
+    <row r="999" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A999" s="1"/>
+    </row>
+    <row r="1000" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1000" s="1"/>
+    </row>
+    <row r="1001" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1001" s="1"/>
+    </row>
+    <row r="1002" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1002" s="1"/>
+    </row>
+    <row r="1003" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1003" s="1"/>
+    </row>
+    <row r="1004" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1004" s="1"/>
+    </row>
+    <row r="1005" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1005" s="1"/>
+    </row>
+    <row r="1006" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1006" s="1"/>
+    </row>
+    <row r="1007" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1007" s="1"/>
+    </row>
+    <row r="1008" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1008" s="1"/>
+    </row>
+    <row r="1009" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1009" s="1"/>
+    </row>
+    <row r="1010" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1010" s="1"/>
+    </row>
+    <row r="1011" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1011" s="1"/>
+    </row>
+    <row r="1012" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1012" s="1"/>
+    </row>
+    <row r="1013" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1013" s="1"/>
+    </row>
+    <row r="1014" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1014" s="1"/>
+    </row>
+    <row r="1015" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1015" s="1"/>
+    </row>
+    <row r="1016" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1016" s="1"/>
+    </row>
+    <row r="1017" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1017" s="1"/>
+    </row>
+    <row r="1018" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1018" s="1"/>
+    </row>
+    <row r="1019" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1019" s="1"/>
+    </row>
+    <row r="1020" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1020" s="1"/>
+    </row>
+    <row r="1021" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1021" s="1"/>
+    </row>
+    <row r="1022" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1022" s="1"/>
+    </row>
+    <row r="1023" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1023" s="1"/>
+    </row>
+    <row r="1024" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1024" s="1"/>
+    </row>
+    <row r="1025" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1025" s="1"/>
+    </row>
+    <row r="1026" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1026" s="1"/>
+    </row>
+    <row r="1027" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1027" s="1"/>
+    </row>
+    <row r="1028" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1028" s="1"/>
+    </row>
+    <row r="1029" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1029" s="1"/>
+    </row>
+    <row r="1030" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1030" s="1"/>
+    </row>
+    <row r="1031" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1031" s="1"/>
+    </row>
+    <row r="1032" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1032" s="1"/>
+    </row>
+    <row r="1033" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1033" s="1"/>
+    </row>
+    <row r="1034" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1034" s="1"/>
+    </row>
+    <row r="1035" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1035" s="1"/>
+    </row>
+    <row r="1036" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1036" s="1"/>
+    </row>
+    <row r="1037" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1037" s="1"/>
+    </row>
+    <row r="1038" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1038" s="1"/>
+    </row>
+    <row r="1039" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1039" s="1"/>
+    </row>
+    <row r="1040" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1040" s="1"/>
+    </row>
+    <row r="1041" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1041" s="1"/>
+    </row>
+    <row r="1042" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1042" s="1"/>
+    </row>
+    <row r="1043" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1043" s="1"/>
+    </row>
+    <row r="1044" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1044" s="1"/>
+    </row>
+    <row r="1045" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1045" s="1"/>
+    </row>
+    <row r="1046" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1046" s="1"/>
+    </row>
+    <row r="1047" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1047" s="1"/>
+    </row>
+    <row r="1048" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1048" s="1"/>
+    </row>
+    <row r="1049" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1049" s="1"/>
+    </row>
+    <row r="1050" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1050" s="1"/>
+    </row>
+    <row r="1051" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1051" s="1"/>
+    </row>
+    <row r="1052" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1052" s="1"/>
+    </row>
+    <row r="1053" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1053" s="1"/>
+    </row>
+    <row r="1054" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1054" s="1"/>
+    </row>
+    <row r="1055" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1055" s="1"/>
+    </row>
+    <row r="1056" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1056" s="1"/>
+    </row>
+    <row r="1057" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1057" s="1"/>
+    </row>
+    <row r="1058" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1058" s="1"/>
+    </row>
+    <row r="1059" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1059" s="1"/>
+    </row>
+    <row r="1060" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1060" s="1"/>
+    </row>
+    <row r="1061" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1061" s="1"/>
+    </row>
+    <row r="1062" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1062" s="1"/>
+    </row>
+    <row r="1063" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1063" s="1"/>
+    </row>
+    <row r="1064" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1064" s="1"/>
+    </row>
+    <row r="1065" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1065" s="1"/>
+    </row>
+    <row r="1066" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1066" s="1"/>
+    </row>
+    <row r="1067" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1067" s="1"/>
+    </row>
+    <row r="1068" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1068" s="1"/>
+    </row>
+    <row r="1069" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1069" s="1"/>
+    </row>
+    <row r="1070" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1070" s="1"/>
+    </row>
+    <row r="1071" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1071" s="1"/>
+    </row>
+    <row r="1072" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1072" s="1"/>
+    </row>
+    <row r="1073" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1073" s="1"/>
+    </row>
+    <row r="1074" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1074" s="1"/>
+    </row>
+    <row r="1075" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1075" s="1"/>
+    </row>
+    <row r="1076" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1076" s="1"/>
+    </row>
+    <row r="1077" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1077" s="1"/>
+    </row>
+    <row r="1078" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1078" s="1"/>
+    </row>
+    <row r="1079" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1079" s="1"/>
+    </row>
+    <row r="1080" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1080" s="1"/>
+    </row>
+    <row r="1081" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1081" s="1"/>
+    </row>
+    <row r="1082" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1082" s="1"/>
+    </row>
+    <row r="1083" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1083" s="1"/>
+    </row>
+    <row r="1084" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1084" s="1"/>
+    </row>
+    <row r="1085" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1085" s="1"/>
+    </row>
+    <row r="1086" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1086" s="1"/>
+    </row>
+    <row r="1087" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1087" s="1"/>
+    </row>
+    <row r="1088" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1088" s="1"/>
+    </row>
+    <row r="1089" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1089" s="1"/>
+    </row>
+    <row r="1090" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1090" s="1"/>
+    </row>
+    <row r="1091" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1091" s="1"/>
+    </row>
+    <row r="1092" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1092" s="1"/>
+    </row>
+    <row r="1093" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1093" s="1"/>
+    </row>
+    <row r="1094" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1094" s="1"/>
+    </row>
+    <row r="1095" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1095" s="1"/>
+    </row>
+    <row r="1096" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1096" s="1"/>
+    </row>
+    <row r="1097" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1097" s="1"/>
+    </row>
+    <row r="1098" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1098" s="1"/>
+    </row>
+    <row r="1099" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1099" s="1"/>
+    </row>
+    <row r="1100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1100" s="1"/>
+    </row>
+    <row r="1101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1101" s="1"/>
+    </row>
+    <row r="1102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1102" s="1"/>
+    </row>
+    <row r="1103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1103" s="1"/>
+    </row>
+    <row r="1104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1104" s="1"/>
+    </row>
+    <row r="1105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1105" s="1"/>
+    </row>
+    <row r="1106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1106" s="1"/>
+    </row>
+    <row r="1107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1107" s="1"/>
+    </row>
+    <row r="1108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1108" s="1"/>
+    </row>
+    <row r="1109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1109" s="1"/>
+    </row>
+    <row r="1110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1110" s="1"/>
+    </row>
+    <row r="1111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1111" s="1"/>
+    </row>
+    <row r="1112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1112" s="1"/>
+    </row>
+    <row r="1113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1113" s="1"/>
+    </row>
+    <row r="1114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1114" s="1"/>
+    </row>
+    <row r="1115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1115" s="1"/>
+    </row>
+    <row r="1116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1116" s="1"/>
+    </row>
+    <row r="1117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1117" s="1"/>
+    </row>
+    <row r="1118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1118" s="1"/>
+    </row>
+    <row r="1119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1119" s="1"/>
+    </row>
+    <row r="1120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1120" s="1"/>
+    </row>
+    <row r="1121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1121" s="1"/>
+    </row>
+    <row r="1122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1122" s="1"/>
+    </row>
+    <row r="1123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1123" s="1"/>
+    </row>
+    <row r="1124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1124" s="1"/>
+    </row>
+    <row r="1125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1125" s="1"/>
+    </row>
+    <row r="1126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1126" s="1"/>
+    </row>
+    <row r="1127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1127" s="1"/>
+    </row>
+    <row r="1128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1128" s="1"/>
+    </row>
+    <row r="1129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1129" s="1"/>
+    </row>
+    <row r="1130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1130" s="1"/>
+    </row>
+    <row r="1131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1131" s="1"/>
+    </row>
+    <row r="1132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1132" s="1"/>
+    </row>
+    <row r="1133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1133" s="1"/>
+    </row>
+    <row r="1134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1134" s="1"/>
+    </row>
+    <row r="1135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1135" s="1"/>
+    </row>
+    <row r="1136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1136" s="1"/>
+    </row>
+    <row r="1137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1137" s="1"/>
+    </row>
+    <row r="1138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1138" s="1"/>
+    </row>
+    <row r="1139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1139" s="1"/>
+    </row>
+    <row r="1140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1140" s="1"/>
+    </row>
+    <row r="1141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1141" s="1"/>
+    </row>
+    <row r="1142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1142" s="1"/>
+    </row>
+    <row r="1143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1143" s="1"/>
+    </row>
+    <row r="1144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1144" s="1"/>
+    </row>
+    <row r="1145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1145" s="1"/>
+    </row>
+    <row r="1146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1146" s="1"/>
+    </row>
+    <row r="1147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1147" s="1"/>
+    </row>
+    <row r="1148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1148" s="1"/>
+    </row>
+    <row r="1149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1149" s="1"/>
+    </row>
+    <row r="1150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1150" s="1"/>
+    </row>
+    <row r="1151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1151" s="1"/>
+    </row>
+    <row r="1152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1152" s="1"/>
+    </row>
+    <row r="1153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1153" s="1"/>
+    </row>
+    <row r="1154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1154" s="1"/>
+    </row>
+    <row r="1155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1155" s="1"/>
+    </row>
+    <row r="1156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1156" s="1"/>
+    </row>
+    <row r="1157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1157" s="1"/>
+    </row>
+    <row r="1158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1158" s="1"/>
+    </row>
+    <row r="1159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1159" s="1"/>
+    </row>
+    <row r="1160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1160" s="1"/>
+    </row>
+    <row r="1161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1161" s="1"/>
+    </row>
+    <row r="1162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1162" s="1"/>
+    </row>
+    <row r="1163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1163" s="1"/>
+    </row>
+    <row r="1164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1164" s="1"/>
+    </row>
+    <row r="1165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1165" s="1"/>
+    </row>
+    <row r="1166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1166" s="1"/>
+    </row>
+    <row r="1167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1167" s="1"/>
+    </row>
+    <row r="1168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1168" s="1"/>
+    </row>
+    <row r="1169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1169" s="1"/>
+    </row>
+    <row r="1170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1170" s="1"/>
+    </row>
+    <row r="1171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1171" s="1"/>
+    </row>
+    <row r="1172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1172" s="1"/>
+    </row>
+    <row r="1173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1173" s="1"/>
+    </row>
+    <row r="1174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1174" s="1"/>
+    </row>
+    <row r="1175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1175" s="1"/>
+    </row>
+    <row r="1176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1176" s="1"/>
+    </row>
+    <row r="1177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1177" s="1"/>
+    </row>
+    <row r="1178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1178" s="1"/>
+    </row>
+    <row r="1179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1179" s="1"/>
+    </row>
+    <row r="1180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1180" s="1"/>
+    </row>
+    <row r="1181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1181" s="1"/>
+    </row>
+    <row r="1182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1182" s="1"/>
+    </row>
+    <row r="1183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1183" s="1"/>
+    </row>
+    <row r="1184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1184" s="1"/>
+    </row>
+    <row r="1185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1185" s="1"/>
+    </row>
+    <row r="1186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1186" s="1"/>
+    </row>
+    <row r="1187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1187" s="1"/>
+    </row>
+    <row r="1188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1188" s="1"/>
+    </row>
+    <row r="1189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1189" s="1"/>
+    </row>
+    <row r="1190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1190" s="1"/>
+    </row>
+    <row r="1191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1191" s="1"/>
+    </row>
+    <row r="1192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1192" s="1"/>
+    </row>
+    <row r="1193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1193" s="1"/>
+    </row>
+    <row r="1194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1194" s="1"/>
+    </row>
+    <row r="1195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1195" s="1"/>
+    </row>
+    <row r="1196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1"/>
+    </row>
+    <row r="1197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1197" s="1"/>
+    </row>
+    <row r="1198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1198" s="1"/>
+    </row>
+    <row r="1199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1199" s="1"/>
+    </row>
+    <row r="1200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1200" s="1"/>
+    </row>
+    <row r="1201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1201" s="1"/>
+    </row>
+    <row r="1202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1202" s="1"/>
+    </row>
+    <row r="1203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1203" s="1"/>
+    </row>
+    <row r="1204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1204" s="1"/>
+    </row>
+    <row r="1205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1205" s="1"/>
+    </row>
+    <row r="1206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1206" s="1"/>
+    </row>
+    <row r="1207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1207" s="1"/>
+    </row>
+    <row r="1208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1208" s="1"/>
+    </row>
+    <row r="1209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1209" s="1"/>
+    </row>
+    <row r="1210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1210" s="1"/>
+    </row>
+    <row r="1211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1211" s="1"/>
+    </row>
+    <row r="1212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1212" s="1"/>
+    </row>
+    <row r="1213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1213" s="1"/>
+    </row>
+    <row r="1214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1214" s="1"/>
+    </row>
+    <row r="1215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1215" s="1"/>
+    </row>
+    <row r="1216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1216" s="1"/>
+    </row>
+    <row r="1217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1217" s="1"/>
+    </row>
+    <row r="1218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1218" s="1"/>
+    </row>
+    <row r="1219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1219" s="1"/>
+    </row>
+    <row r="1220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1220" s="1"/>
+    </row>
+    <row r="1221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1221" s="1"/>
+    </row>
+    <row r="1222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1222" s="1"/>
+    </row>
+    <row r="1223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1223" s="1"/>
+    </row>
+    <row r="1224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1224" s="1"/>
+    </row>
+    <row r="1225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1225" s="1"/>
+    </row>
+    <row r="1226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1226" s="1"/>
+    </row>
+    <row r="1227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1227" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17835,7 +14035,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T1227"/>
+  <dimension ref="A1:T1234"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -17902,7 +14102,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <f>_xll.BQL($B$1:$T$1,"dropna(px_last(fill=PREV,dates=range(2023-01-02,2026-05-11)))","showids","false","showheaders","false","showallcols","false","cols=20;rows=1226")</f>
+        <f>_xll.BQL($B$1:$T$1,"dropna(px_last(fill=PREV,dates=range(2023-01-02,2026-05-18)))","showids","false","showheaders","false","showallcols","false","cols=20;rows=1233")</f>
         <v>44928</v>
       </c>
       <c r="B2">
@@ -93856,61 +90056,495 @@
         <v>46153</v>
       </c>
       <c r="B1227">
-        <v>4.3882360458374023</v>
+        <v>4.4134435649999997</v>
       </c>
       <c r="C1227">
-        <v>98.037002563476563</v>
+        <v>97.954999999999998</v>
       </c>
       <c r="D1227">
-        <v>7398.93</v>
+        <v>7412.84</v>
       </c>
       <c r="E1227">
-        <v>140.19409999999999</v>
+        <v>141.19589999999999</v>
       </c>
       <c r="F1227">
-        <v>2.6600000860000002</v>
+        <v>2.6400001049999999</v>
       </c>
       <c r="G1227">
-        <v>46.407890319824219</v>
+        <v>45.779037475999999</v>
       </c>
       <c r="H1227">
-        <v>2.4658784866333008</v>
+        <v>2.4838905329999998</v>
       </c>
       <c r="I1227">
-        <v>8266.77</v>
+        <v>8259.86</v>
       </c>
       <c r="J1227">
-        <v>17.190000000000001</v>
+        <v>18.38</v>
       </c>
       <c r="K1227">
-        <v>47.758000000000003</v>
+        <v>47.685000000000002</v>
       </c>
       <c r="L1227">
-        <v>-20.4175</v>
+        <v>-20.375</v>
       </c>
       <c r="M1227">
-        <v>630.00001907348633</v>
+        <v>641.35</v>
       </c>
       <c r="N1227">
-        <v>99.220001220703125</v>
+        <v>98.07</v>
       </c>
       <c r="O1227">
-        <v>4703.10009765625</v>
+        <v>4728.7</v>
       </c>
       <c r="P1227">
-        <v>1197</v>
+        <v>1199.75</v>
       </c>
       <c r="Q1227">
-        <v>0.77</v>
+        <v>0.76</v>
       </c>
       <c r="R1227">
-        <v>56.432650000000002</v>
+        <v>56.262509999999999</v>
       </c>
       <c r="S1227">
-        <v>67.25</v>
+        <v>70.739999999999995</v>
       </c>
       <c r="T1227">
-        <v>1.915736198425293</v>
+        <v>1.926433563</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1228" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B1228">
+        <v>4.4629840850000004</v>
+      </c>
+      <c r="C1228">
+        <v>98.298000000000002</v>
+      </c>
+      <c r="D1228">
+        <v>7400.96</v>
+      </c>
+      <c r="E1228">
+        <v>143.13040000000001</v>
+      </c>
+      <c r="F1228">
+        <v>2.6800000669999999</v>
+      </c>
+      <c r="G1228">
+        <v>46.944904327000003</v>
+      </c>
+      <c r="H1228">
+        <v>2.4950675960000002</v>
+      </c>
+      <c r="I1228">
+        <v>8250.11</v>
+      </c>
+      <c r="J1228">
+        <v>17.989999999999998</v>
+      </c>
+      <c r="K1228">
+        <v>47.643999999999998</v>
+      </c>
+      <c r="L1228">
+        <v>-20.625</v>
+      </c>
+      <c r="M1228">
+        <v>648.5</v>
+      </c>
+      <c r="N1228">
+        <v>102.18</v>
+      </c>
+      <c r="O1228">
+        <v>4686.7</v>
+      </c>
+      <c r="P1228">
+        <v>1213.5</v>
+      </c>
+      <c r="Q1228">
+        <v>0.76</v>
+      </c>
+      <c r="R1228">
+        <v>58.117750000000001</v>
+      </c>
+      <c r="S1228">
+        <v>71.680000000000007</v>
+      </c>
+      <c r="T1228">
+        <v>1.9648427959999999</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1229" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1229">
+        <v>4.4688234329999998</v>
+      </c>
+      <c r="C1229">
+        <v>98.524000000000001</v>
+      </c>
+      <c r="D1229">
+        <v>7444.25</v>
+      </c>
+      <c r="E1229">
+        <v>143.1087</v>
+      </c>
+      <c r="F1229">
+        <v>2.670000076</v>
+      </c>
+      <c r="G1229">
+        <v>48.548603057999998</v>
+      </c>
+      <c r="H1229">
+        <v>2.496792793</v>
+      </c>
+      <c r="I1229">
+        <v>8214.7999999999993</v>
+      </c>
+      <c r="J1229">
+        <v>17.87</v>
+      </c>
+      <c r="K1229">
+        <v>47.598999999999997</v>
+      </c>
+      <c r="L1229">
+        <v>-20.375</v>
+      </c>
+      <c r="M1229">
+        <v>663.55000000000007</v>
+      </c>
+      <c r="N1229">
+        <v>101.02</v>
+      </c>
+      <c r="O1229">
+        <v>4706.7</v>
+      </c>
+      <c r="P1229">
+        <v>1215.25</v>
+      </c>
+      <c r="Q1229">
+        <v>0.75</v>
+      </c>
+      <c r="R1229">
+        <v>57.144620000000003</v>
+      </c>
+      <c r="S1229">
+        <v>70.239999999999995</v>
+      </c>
+      <c r="T1229">
+        <v>1.963077545</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1230" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1230">
+        <v>4.4815940860000003</v>
+      </c>
+      <c r="C1230">
+        <v>98.819010000000006</v>
+      </c>
+      <c r="D1230">
+        <v>7501.24</v>
+      </c>
+      <c r="E1230">
+        <v>141.47919999999999</v>
+      </c>
+      <c r="F1230">
+        <v>2.6400001049999999</v>
+      </c>
+      <c r="G1230">
+        <v>45.8111763</v>
+      </c>
+      <c r="H1230">
+        <v>2.4894075390000001</v>
+      </c>
+      <c r="I1230">
+        <v>8245.36</v>
+      </c>
+      <c r="J1230">
+        <v>17.260000000000002</v>
+      </c>
+      <c r="K1230">
+        <v>47.463999999999999</v>
+      </c>
+      <c r="L1230">
+        <v>-20.125</v>
+      </c>
+      <c r="M1230">
+        <v>656.75</v>
+      </c>
+      <c r="N1230">
+        <v>101.17</v>
+      </c>
+      <c r="O1230">
+        <v>4685.3</v>
+      </c>
+      <c r="P1230">
+        <v>1174.5</v>
+      </c>
+      <c r="Q1230">
+        <v>0.74</v>
+      </c>
+      <c r="R1230">
+        <v>56.2684</v>
+      </c>
+      <c r="S1230">
+        <v>69.63</v>
+      </c>
+      <c r="T1230">
+        <v>1.983704567</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1231" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1231">
+        <v>4.5933504100000002</v>
+      </c>
+      <c r="C1231">
+        <v>99.284000000000006</v>
+      </c>
+      <c r="D1231">
+        <v>7408.5</v>
+      </c>
+      <c r="E1231">
+        <v>140.91120000000001</v>
+      </c>
+      <c r="F1231">
+        <v>2.670000076</v>
+      </c>
+      <c r="G1231">
+        <v>51.827335357999999</v>
+      </c>
+      <c r="H1231">
+        <v>2.5146808620000001</v>
+      </c>
+      <c r="I1231">
+        <v>8156.09</v>
+      </c>
+      <c r="J1231">
+        <v>18.43</v>
+      </c>
+      <c r="K1231">
+        <v>47.19</v>
+      </c>
+      <c r="L1231">
+        <v>-20.75</v>
+      </c>
+      <c r="M1231">
+        <v>625.15</v>
+      </c>
+      <c r="N1231">
+        <v>105.42</v>
+      </c>
+      <c r="O1231">
+        <v>4561.8999999999996</v>
+      </c>
+      <c r="P1231">
+        <v>1177</v>
+      </c>
+      <c r="Q1231">
+        <v>0.73</v>
+      </c>
+      <c r="R1231">
+        <v>58.142090000000003</v>
+      </c>
+      <c r="S1231">
+        <v>79.87</v>
+      </c>
+      <c r="T1231">
+        <v>2.069402695</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1232" s="1">
+        <v>46158</v>
+      </c>
+      <c r="B1232">
+        <v>4.5933504100000002</v>
+      </c>
+      <c r="C1232">
+        <v>99.284000000000006</v>
+      </c>
+      <c r="D1232">
+        <v>7408.5</v>
+      </c>
+      <c r="E1232">
+        <v>140.91120000000001</v>
+      </c>
+      <c r="F1232">
+        <v>2.670000076</v>
+      </c>
+      <c r="G1232">
+        <v>51.827335357999999</v>
+      </c>
+      <c r="H1232">
+        <v>2.5146808620000001</v>
+      </c>
+      <c r="I1232">
+        <v>8156.09</v>
+      </c>
+      <c r="J1232">
+        <v>18.43</v>
+      </c>
+      <c r="K1232">
+        <v>47.19</v>
+      </c>
+      <c r="L1232">
+        <v>-20.75</v>
+      </c>
+      <c r="M1232">
+        <v>625.15</v>
+      </c>
+      <c r="N1232">
+        <v>105.42</v>
+      </c>
+      <c r="O1232">
+        <v>4561.8999999999996</v>
+      </c>
+      <c r="P1232">
+        <v>1177</v>
+      </c>
+      <c r="Q1232">
+        <v>0.73</v>
+      </c>
+      <c r="R1232">
+        <v>58.142090000000003</v>
+      </c>
+      <c r="S1232">
+        <v>79.87</v>
+      </c>
+      <c r="T1232">
+        <v>2.069402695</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1233" s="1">
+        <v>46159</v>
+      </c>
+      <c r="B1233">
+        <v>4.5933504100000002</v>
+      </c>
+      <c r="C1233">
+        <v>99.284000000000006</v>
+      </c>
+      <c r="D1233">
+        <v>7408.5</v>
+      </c>
+      <c r="E1233">
+        <v>140.91120000000001</v>
+      </c>
+      <c r="F1233">
+        <v>2.670000076</v>
+      </c>
+      <c r="G1233">
+        <v>51.827335357999999</v>
+      </c>
+      <c r="H1233">
+        <v>2.5146808620000001</v>
+      </c>
+      <c r="I1233">
+        <v>8156.09</v>
+      </c>
+      <c r="J1233">
+        <v>18.43</v>
+      </c>
+      <c r="K1233">
+        <v>47.19</v>
+      </c>
+      <c r="L1233">
+        <v>-20.75</v>
+      </c>
+      <c r="M1233">
+        <v>625.15</v>
+      </c>
+      <c r="N1233">
+        <v>105.42</v>
+      </c>
+      <c r="O1233">
+        <v>4561.8999999999996</v>
+      </c>
+      <c r="P1233">
+        <v>1177</v>
+      </c>
+      <c r="Q1233">
+        <v>0.73</v>
+      </c>
+      <c r="R1233">
+        <v>58.142090000000003</v>
+      </c>
+      <c r="S1233">
+        <v>79.87</v>
+      </c>
+      <c r="T1233">
+        <v>2.069402695</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1234" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1234">
+        <v>4.6272048950195313</v>
+      </c>
+      <c r="C1234">
+        <v>99.357002258300781</v>
+      </c>
+      <c r="D1234">
+        <v>7408.5</v>
+      </c>
+      <c r="E1234">
+        <v>142.06890000000001</v>
+      </c>
+      <c r="F1234">
+        <v>2.670000076</v>
+      </c>
+      <c r="G1234">
+        <v>52.890300750732422</v>
+      </c>
+      <c r="H1234">
+        <v>2.5146808620000001</v>
+      </c>
+      <c r="I1234">
+        <v>8156.09</v>
+      </c>
+      <c r="J1234">
+        <v>18.43</v>
+      </c>
+      <c r="K1234">
+        <v>47.133000000000003</v>
+      </c>
+      <c r="L1234">
+        <v>-21</v>
+      </c>
+      <c r="M1234">
+        <v>625.15</v>
+      </c>
+      <c r="N1234">
+        <v>107.91999816894531</v>
+      </c>
+      <c r="O1234">
+        <v>4527.60009765625</v>
+      </c>
+      <c r="P1234">
+        <v>1194</v>
+      </c>
+      <c r="Q1234">
+        <v>0.73</v>
+      </c>
+      <c r="R1234">
+        <v>58.142090000000003</v>
+      </c>
+      <c r="S1234">
+        <v>79.87</v>
+      </c>
+      <c r="T1234">
+        <v>2.069402695</v>
       </c>
     </row>
   </sheetData>
@@ -93964,22 +90598,22 @@
         <v>25</v>
       </c>
       <c r="B2" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C2">
-        <v>9.6650501860832225</v>
+        <v>-5.8000822706705071</v>
       </c>
       <c r="D2">
-        <v>11.898734177215177</v>
+        <v>-10.152035311427179</v>
       </c>
       <c r="E2">
-        <v>0.60004138216428549</v>
+        <v>-9.2889681124975336</v>
       </c>
       <c r="F2">
-        <v>-7.5577526380834703</v>
+        <v>-8.8647895731768074</v>
       </c>
       <c r="G2">
-        <v>128.42377260981911</v>
+        <v>132.31042353537913</v>
       </c>
       <c r="K2" t="s">
         <v>26</v>
@@ -93990,22 +90624,22 @@
         <v>26</v>
       </c>
       <c r="B3" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C3">
-        <v>-0.13143071723620031</v>
+        <v>-9.2216582064297814</v>
       </c>
       <c r="D3">
-        <v>4.171562867215032</v>
+        <v>-11.832374691865249</v>
       </c>
       <c r="E3">
-        <v>12.571428571428566</v>
+        <v>-4.9788448292826946</v>
       </c>
       <c r="F3">
-        <v>15.731070496083543</v>
+        <v>5.5986878075450965</v>
       </c>
       <c r="G3">
-        <v>173.32990750256937</v>
+        <v>145.6626812515899</v>
       </c>
       <c r="K3" t="s">
         <v>27</v>
@@ -94016,22 +90650,22 @@
         <v>27</v>
       </c>
       <c r="B4" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C4">
-        <v>-1.1819484240687743</v>
+        <v>-9.5143167814425507</v>
       </c>
       <c r="D4">
-        <v>0.74858499178381699</v>
+        <v>-12.755547789620824</v>
       </c>
       <c r="E4">
-        <v>8.2810047095761359</v>
+        <v>-10.615825277479413</v>
       </c>
       <c r="F4">
-        <v>2.7369204989759801</v>
+        <v>-5.7746744668805476</v>
       </c>
       <c r="G4">
-        <v>103.16642120765832</v>
+        <v>80.187657885239986</v>
       </c>
       <c r="K4" t="s">
         <v>28</v>
@@ -94042,22 +90676,22 @@
         <v>28</v>
       </c>
       <c r="B5" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C5">
-        <v>8.5868442199517894</v>
+        <v>-7.6540860556084249</v>
       </c>
       <c r="D5">
-        <v>10.437828371278455</v>
+        <v>-10.502049180327869</v>
       </c>
       <c r="E5">
-        <v>-4.8294597041955907</v>
+        <v>-12.945983655571066</v>
       </c>
       <c r="F5">
-        <v>-10.738888364631496</v>
+        <v>-14.830343213728556</v>
       </c>
       <c r="G5">
-        <v>87.79035139964266</v>
+        <v>88.538743794517586</v>
       </c>
       <c r="K5" t="s">
         <v>29</v>
@@ -94068,22 +90702,22 @@
         <v>29</v>
       </c>
       <c r="B6" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C6">
-        <v>8.7539531941809017</v>
+        <v>-3.3965336745376313</v>
       </c>
       <c r="D6">
-        <v>12.159165035877354</v>
+        <v>-5.1832400959013656</v>
       </c>
       <c r="E6">
-        <v>2.9334291187739501</v>
+        <v>-4.7482509462094287</v>
       </c>
       <c r="F6">
-        <v>-4.6049711495783461</v>
+        <v>-4.165705054234941</v>
       </c>
       <c r="G6">
-        <v>119.53524004085803</v>
+        <v>110.09359979762206</v>
       </c>
       <c r="K6" t="s">
         <v>30</v>
@@ -94094,22 +90728,22 @@
         <v>30</v>
       </c>
       <c r="B7" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C7">
-        <v>4.7589993898718799</v>
+        <v>-1.4560279557367499</v>
       </c>
       <c r="D7">
-        <v>5.6290372193171505</v>
+        <v>-3.0372492836676082</v>
       </c>
       <c r="E7">
-        <v>9.4676442460950021</v>
+        <v>0.74426912771658227</v>
       </c>
       <c r="F7">
-        <v>9.7826086956521809</v>
+        <v>4.9302325581395454</v>
       </c>
       <c r="G7">
-        <v>77.92746113989638</v>
+        <v>61.066158971918142</v>
       </c>
       <c r="K7" t="s">
         <v>31</v>
@@ -94120,22 +90754,22 @@
         <v>31</v>
       </c>
       <c r="B8" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C8">
-        <v>20.398422909317297</v>
+        <v>-1.3960703205791145</v>
       </c>
       <c r="D8">
-        <v>14.891089108910895</v>
+        <v>-2.1549512570548965</v>
       </c>
       <c r="E8">
-        <v>37.520739511732657</v>
+        <v>16.588546973711026</v>
       </c>
       <c r="F8">
-        <v>39.33717579250721</v>
+        <v>42.882117882117889</v>
       </c>
       <c r="G8">
-        <v>273.11897106109325</v>
+        <v>217.83333333333331</v>
       </c>
       <c r="K8" t="s">
         <v>32</v>
@@ -94146,22 +90780,22 @@
         <v>32</v>
       </c>
       <c r="B9" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C9">
-        <v>1.6343552750225459</v>
+        <v>-6.7539092824664557</v>
       </c>
       <c r="D9">
-        <v>3.5009182736455431</v>
+        <v>-8.2296441824929119</v>
       </c>
       <c r="E9">
-        <v>15.750962772785615</v>
+        <v>1.021266370299164</v>
       </c>
       <c r="F9">
-        <v>22.264406779661019</v>
+        <v>13.867822318526537</v>
       </c>
       <c r="G9">
-        <v>139.36819750464559</v>
+        <v>117.9367547952307</v>
       </c>
       <c r="K9" t="s">
         <v>33</v>
@@ -94172,22 +90806,22 @@
         <v>33</v>
       </c>
       <c r="B10" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C10">
-        <v>-2.4550385383956592</v>
+        <v>-6.0384352746073668</v>
       </c>
       <c r="D10">
-        <v>1.0946745562130171</v>
+        <v>-5.1875184565410075</v>
       </c>
       <c r="E10">
-        <v>-1.280816640986131</v>
+        <v>-10.191142191142198</v>
       </c>
       <c r="F10">
-        <v>-14.999999999999991</v>
+        <v>-19.458148674638355</v>
       </c>
       <c r="G10">
-        <v>6.3492063492063542</v>
+        <v>-4.5296857964119415</v>
       </c>
       <c r="K10" t="s">
         <v>34</v>
@@ -94198,22 +90832,22 @@
         <v>34</v>
       </c>
       <c r="B11" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C11">
-        <v>0.59405940594059314</v>
+        <v>-7.6443569553805837</v>
       </c>
       <c r="D11">
-        <v>-0.32701111837801788</v>
+        <v>-5.9786239144956665</v>
       </c>
       <c r="E11">
-        <v>14.242878560719644</v>
+        <v>-8.574212406625529</v>
       </c>
       <c r="F11">
-        <v>6.054279749478086</v>
+        <v>-5.0910316925151768</v>
       </c>
       <c r="G11">
-        <v>44.249881684808337</v>
+        <v>29.12844036697247</v>
       </c>
       <c r="K11" t="s">
         <v>35</v>
@@ -94224,22 +90858,22 @@
         <v>35</v>
       </c>
       <c r="B12" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C12">
-        <v>4.5432576123731296</v>
+        <v>-2.0896902450300554</v>
       </c>
       <c r="D12">
-        <v>5.6668295065950289</v>
+        <v>-2.5492361494570179</v>
       </c>
       <c r="E12">
-        <v>9.718981434513557</v>
+        <v>4.3045705279747883</v>
       </c>
       <c r="F12">
-        <v>5.5533866874878122</v>
+        <v>7.3390775468829137</v>
       </c>
       <c r="G12">
-        <v>76.054045254761533</v>
+        <v>66.769036932041899</v>
       </c>
       <c r="K12" t="s">
         <v>36</v>
@@ -94250,22 +90884,22 @@
         <v>36</v>
       </c>
       <c r="B13" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C13">
-        <v>3.3384195681324265</v>
+        <v>-2.7831222873506638</v>
       </c>
       <c r="D13">
-        <v>4.2737834180935925</v>
+        <v>-3.8585778131775736</v>
       </c>
       <c r="E13">
-        <v>-2.6781048597805159</v>
+        <v>-6.3249116150728577</v>
       </c>
       <c r="F13">
-        <v>-3.2301363931586833</v>
+        <v>-9.5913781624500594</v>
       </c>
       <c r="G13">
-        <v>36.833404763362516</v>
+        <v>26.363847853902534</v>
       </c>
       <c r="K13" t="s">
         <v>37</v>
@@ -94276,22 +90910,22 @@
         <v>37</v>
       </c>
       <c r="B14" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C14">
-        <v>-5.3525913338997428</v>
+        <v>6.7145421903051963</v>
       </c>
       <c r="D14">
-        <v>-6.2131671998652926</v>
+        <v>3.9706139583697677</v>
       </c>
       <c r="E14">
-        <v>-2.1777309448542237</v>
+        <v>8.0334423845874117</v>
       </c>
       <c r="F14">
-        <v>1.3095671153146708</v>
+        <v>8.506754289886814</v>
       </c>
       <c r="G14">
-        <v>35.144971490962021</v>
+        <v>39.073467477772567</v>
       </c>
       <c r="K14" t="s">
         <v>38</v>
@@ -94302,22 +90936,22 @@
         <v>38</v>
       </c>
       <c r="B15" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C15">
-        <v>11.125495272841389</v>
+        <v>-1.8004024428989889</v>
       </c>
       <c r="D15">
-        <v>11.789893249669477</v>
+        <v>-3.4651489649667568</v>
       </c>
       <c r="E15">
-        <v>29.678630287493124</v>
+        <v>19.859531196139262</v>
       </c>
       <c r="F15">
-        <v>36.588070784512269</v>
+        <v>34.853957096109568</v>
       </c>
       <c r="G15">
-        <v>153.59892569382271</v>
+        <v>125.76901225549877</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
@@ -94328,22 +90962,22 @@
         <v>39</v>
       </c>
       <c r="B16" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C16">
-        <v>4.2967631051276337E-2</v>
+        <v>-4.1231209735146681</v>
       </c>
       <c r="D16">
-        <v>1.2465574720974046</v>
+        <v>-2.3048869438366131</v>
       </c>
       <c r="E16">
-        <v>1.3199883957064065</v>
+        <v>-4.8316043768651493</v>
       </c>
       <c r="F16">
-        <v>-2.7294248711878679</v>
+        <v>-6.1782011768002194</v>
       </c>
       <c r="G16">
-        <v>23.453517143867085</v>
+        <v>13.048615800135039</v>
       </c>
       <c r="K16" t="s">
         <v>40</v>
@@ -94354,22 +90988,22 @@
         <v>40</v>
       </c>
       <c r="B17" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C17">
-        <v>0.4673807205452814</v>
+        <v>-2.5004845900368409</v>
       </c>
       <c r="D17">
-        <v>1.8558736426456168</v>
+        <v>-3.7504783773440504</v>
       </c>
       <c r="E17">
-        <v>-0.71208622016935619</v>
+        <v>-3.045489591364698</v>
       </c>
       <c r="F17">
-        <v>-3.7859007832898062</v>
+        <v>-5.1301395699736059</v>
       </c>
       <c r="G17">
-        <v>22.019867549668877</v>
+        <v>15.565766800689257</v>
       </c>
       <c r="K17" t="s">
         <v>41</v>
@@ -94380,22 +91014,22 @@
         <v>41</v>
       </c>
       <c r="B18" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C18">
-        <v>1.1880717595348837E-2</v>
+        <v>0.54644808743168649</v>
       </c>
       <c r="D18">
-        <v>0.76610007182188233</v>
+        <v>1.5233297349166319</v>
       </c>
       <c r="E18">
-        <v>2.1974019667354643</v>
+        <v>2.6437060392917862</v>
       </c>
       <c r="F18">
-        <v>-4.7737556561085954</v>
+        <v>-3.8618809631985522</v>
       </c>
       <c r="G18">
-        <v>4.0415276232851447</v>
+        <v>3.1314731326916139</v>
       </c>
       <c r="K18" t="s">
         <v>42</v>
@@ -94406,22 +91040,22 @@
         <v>42</v>
       </c>
       <c r="B19" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C19">
-        <v>-1.0049076887123154</v>
+        <v>-6.6454202077431486</v>
       </c>
       <c r="D19">
-        <v>1.3275923932543947</v>
+        <v>-3.1471956894440281</v>
       </c>
       <c r="E19">
-        <v>2.4054152060921008</v>
+        <v>-9.0396779758481873</v>
       </c>
       <c r="F19">
-        <v>-2.9219663114472296</v>
+        <v>-10.186236656824891</v>
       </c>
       <c r="G19">
-        <v>20.375106564364884</v>
+        <v>3.4261802013861704</v>
       </c>
       <c r="K19" t="s">
         <v>43</v>
@@ -94432,22 +91066,22 @@
         <v>43</v>
       </c>
       <c r="B20" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C20">
-        <v>0.13876040703051612</v>
+        <v>-1.0392609699768955</v>
       </c>
       <c r="D20">
-        <v>1.2983974733886998</v>
+        <v>-2.0795246800731184</v>
       </c>
       <c r="E20">
-        <v>0.97947761194028593</v>
+        <v>-1.2160682381418855</v>
       </c>
       <c r="F20">
-        <v>-0.93800045756120731</v>
+        <v>-2.0795246800731184</v>
       </c>
       <c r="G20">
-        <v>27.25001836749686</v>
+        <v>19.209904020030606</v>
       </c>
       <c r="K20" t="s">
         <v>44</v>
@@ -94458,22 +91092,22 @@
         <v>44</v>
       </c>
       <c r="B21" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C21">
-        <v>3.2893727955835153</v>
+        <v>-2.9841882562541828</v>
       </c>
       <c r="D21">
-        <v>0.90636704119850786</v>
+        <v>-3.0129870129870144</v>
       </c>
       <c r="E21">
-        <v>4.0713844252163245</v>
+        <v>-5.7546693589096343</v>
       </c>
       <c r="F21">
-        <v>8.0705976734857625</v>
+        <v>4.0525477707006399</v>
       </c>
       <c r="G21">
-        <v>76.345071344416809</v>
+        <v>65.388509238167558</v>
       </c>
       <c r="K21" t="s">
         <v>45</v>
@@ -94484,22 +91118,22 @@
         <v>45</v>
       </c>
       <c r="B22" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C22">
-        <v>7.2057409188429453</v>
+        <v>-1.262852805189417</v>
       </c>
       <c r="D22">
-        <v>6.7949001400250566</v>
+        <v>-3.2066026248139501</v>
       </c>
       <c r="E22">
-        <v>24.183734681635102</v>
+        <v>11.877394636015334</v>
       </c>
       <c r="F22">
-        <v>21.670864819479434</v>
+        <v>22.332421340629292</v>
       </c>
       <c r="G22">
-        <v>80.843629102708107</v>
+        <v>68.786127167630085</v>
       </c>
       <c r="K22" t="s">
         <v>46</v>
@@ -94510,22 +91144,22 @@
         <v>46</v>
       </c>
       <c r="B23" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C23">
-        <v>5.9410572275066311</v>
+        <v>-4.2243155725640333</v>
       </c>
       <c r="D23">
-        <v>5.9906396255850289</v>
+        <v>-4.1537781705700505</v>
       </c>
       <c r="E23">
-        <v>12.186261558784668</v>
+        <v>2.2470144563167702</v>
       </c>
       <c r="F23">
-        <v>10.363872644574391</v>
+        <v>6.340905376695531</v>
       </c>
       <c r="G23">
-        <v>51.280338454687154</v>
+        <v>40.66147859922178</v>
       </c>
       <c r="K23" t="s">
         <v>47</v>
@@ -94536,22 +91170,22 @@
         <v>47</v>
       </c>
       <c r="B24" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C24">
-        <v>-2.475247524751983E-2</v>
+        <v>-0.87893042832385238</v>
       </c>
       <c r="D24">
-        <v>4.0845251900528305</v>
+        <v>1.2490632025969152E-2</v>
       </c>
       <c r="E24">
-        <v>4.4073930464004087</v>
+        <v>-2.1986075485525971</v>
       </c>
       <c r="F24">
-        <v>-0.82259054634745454</v>
+        <v>-2.1268793546021381</v>
       </c>
       <c r="G24">
-        <v>27.574226152874292</v>
+        <v>17.044291770209028</v>
       </c>
       <c r="K24" t="s">
         <v>48</v>
@@ -94562,22 +91196,22 @@
         <v>48</v>
       </c>
       <c r="B25" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C25">
-        <v>5.6626800097632417</v>
+        <v>-1.8364518364518405</v>
       </c>
       <c r="D25">
-        <v>6.7834237789837202</v>
+        <v>-2.3327970581475537</v>
       </c>
       <c r="E25">
-        <v>17.348875033884518</v>
+        <v>7.0942540322580587</v>
       </c>
       <c r="F25">
-        <v>13.443396226415102</v>
+        <v>9.5514307811291523</v>
       </c>
       <c r="G25">
-        <v>61.77130044843048</v>
+        <v>50.451407328730738</v>
       </c>
       <c r="K25" t="s">
         <v>49</v>
@@ -94588,22 +91222,22 @@
         <v>49</v>
       </c>
       <c r="B26" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C26">
-        <v>0.20306859205775338</v>
+        <v>-2.6570592208961941</v>
       </c>
       <c r="D26">
-        <v>0.74863883847549528</v>
+        <v>-3.0065066188018923</v>
       </c>
       <c r="E26">
-        <v>3.7132181223727141</v>
+        <v>-2.8102517985611515</v>
       </c>
       <c r="F26">
-        <v>3.7616822429906529</v>
+        <v>-0.27681660899655025</v>
       </c>
       <c r="G26">
-        <v>6.7291516462388774</v>
+        <v>2.9040704594144229</v>
       </c>
       <c r="K26" t="s">
         <v>50</v>
@@ -94614,22 +91248,22 @@
         <v>50</v>
       </c>
       <c r="B27" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C27">
-        <v>7.383419689119175</v>
+        <v>-2.9433051869722697</v>
       </c>
       <c r="D27">
-        <v>7.9989577905158944</v>
+        <v>-2.6143790849673332</v>
       </c>
       <c r="E27">
-        <v>16.991250352808361</v>
+        <v>7.5380914194065767</v>
       </c>
       <c r="F27">
-        <v>8.7355718782791332</v>
+        <v>4.8748696558915467</v>
       </c>
       <c r="G27">
-        <v>41.274710293115213</v>
+        <v>28.921647171927571</v>
       </c>
       <c r="K27" t="s">
         <v>51</v>
@@ -94640,22 +91274,22 @@
         <v>51</v>
       </c>
       <c r="B28" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C28">
-        <v>6.6770186335403672</v>
+        <v>-6.9868995633187838</v>
       </c>
       <c r="D28">
-        <v>8.1038552321007025</v>
+        <v>-3.9458850056369816</v>
       </c>
       <c r="E28">
-        <v>6.1413673232908454</v>
+        <v>-8.4527220630372604</v>
       </c>
       <c r="F28">
-        <v>-8.0013391362571156</v>
+        <v>-15.643564356435649</v>
       </c>
       <c r="G28">
-        <v>25.824175824175828</v>
+        <v>12.401055408970979</v>
       </c>
       <c r="K28" t="s">
         <v>52</v>
@@ -94666,22 +91300,22 @@
         <v>52</v>
       </c>
       <c r="B29" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C29">
-        <v>1.3234426367697947</v>
+        <v>-3.0532445923460911</v>
       </c>
       <c r="D29">
-        <v>2.1066938498131194</v>
+        <v>-2.3791572421881573</v>
       </c>
       <c r="E29">
-        <v>6.4753299672247344</v>
+        <v>-3.2223237272651737</v>
       </c>
       <c r="F29">
-        <v>2.0720108695652155</v>
+        <v>-0.41873184071098524</v>
       </c>
       <c r="G29">
-        <v>18.768835531841315</v>
+        <v>7.0703358294666314</v>
       </c>
       <c r="K29" t="s">
         <v>53</v>
@@ -94692,22 +91326,22 @@
         <v>53</v>
       </c>
       <c r="B30" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C30">
-        <v>-1.1504546707081755</v>
+        <v>1.1220294097149524</v>
       </c>
       <c r="D30">
-        <v>-0.85676777447659824</v>
+        <v>1.4401565995525742</v>
       </c>
       <c r="E30">
-        <v>-2.5931708641640032</v>
+        <v>-2.4865591397849576</v>
       </c>
       <c r="F30">
-        <v>-8.1663999999999941</v>
+        <v>-7.9723473076679099</v>
       </c>
       <c r="G30">
-        <v>8.1474223696110961</v>
+        <v>9.023968742955887</v>
       </c>
       <c r="K30" t="s">
         <v>54</v>
@@ -94718,22 +91352,22 @@
         <v>54</v>
       </c>
       <c r="B31" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C31">
-        <v>0.54900128489662292</v>
+        <v>-2.8113382899628272</v>
       </c>
       <c r="D31">
-        <v>1.3182674199623405</v>
+        <v>-2.2206638616175849</v>
       </c>
       <c r="E31">
-        <v>-0.47404324199329012</v>
+        <v>-3.9163891122085639</v>
       </c>
       <c r="F31">
-        <v>-2.2484669543493117</v>
+        <v>-6.5564615212777886</v>
       </c>
       <c r="G31">
-        <v>-1.1143021252153922</v>
+        <v>-3.0590961761297808</v>
       </c>
       <c r="K31" t="s">
         <v>55</v>
@@ -94744,22 +91378,22 @@
         <v>55</v>
       </c>
       <c r="B32" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C32">
-        <v>-2.9504950495049544</v>
+        <v>-1.122219955111196</v>
       </c>
       <c r="D32">
-        <v>-1.8425796114560418</v>
+        <v>1.9137749737118899</v>
       </c>
       <c r="E32">
-        <v>-7.9451540195341925</v>
+        <v>-10.623386204352633</v>
       </c>
       <c r="F32">
-        <v>-16.393722279085637</v>
+        <v>-18.486122792262407</v>
       </c>
       <c r="G32">
-        <v>-19.285243741765481</v>
+        <v>-22.920311754413866</v>
       </c>
       <c r="K32" t="s">
         <v>56</v>
@@ -94770,22 +91404,22 @@
         <v>56</v>
       </c>
       <c r="B33" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C33">
-        <v>2.6754690757470447</v>
+        <v>-4.670050761421316</v>
       </c>
       <c r="D33">
-        <v>3.3578174186778624</v>
+        <v>-4.7989185535653869</v>
       </c>
       <c r="E33">
-        <v>2.9616724738676008</v>
+        <v>-7.4876847290640312</v>
       </c>
       <c r="F33">
-        <v>-13.343108504398829</v>
+        <v>-14.350866524779565</v>
       </c>
       <c r="G33">
-        <v>-10.26419678105071</v>
+        <v>-17.871720116618064</v>
       </c>
       <c r="K33" t="s">
         <v>57</v>
@@ -94796,22 +91430,22 @@
         <v>57</v>
       </c>
       <c r="B34" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C34">
-        <v>-3.9312567132115972</v>
+        <v>-1.9007155635062642</v>
       </c>
       <c r="D34">
-        <v>-3.558335130472285</v>
+        <v>-2.8134692069118366</v>
       </c>
       <c r="E34">
-        <v>-4.7700170357751324</v>
+        <v>-4.9610051993067579</v>
       </c>
       <c r="F34">
-        <v>0.29154518950436292</v>
+        <v>-3.8149528612146502</v>
       </c>
       <c r="G34">
-        <v>11.465603190428718</v>
+        <v>6.7656364078851148</v>
       </c>
       <c r="K34" t="s">
         <v>58</v>
@@ -94822,22 +91456,22 @@
         <v>58</v>
       </c>
       <c r="B35" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C35">
-        <v>1.5611008298012035</v>
+        <v>-4.4868269129841423</v>
       </c>
       <c r="D35">
-        <v>2.1546076263716936</v>
+        <v>-2.8864461045891132</v>
       </c>
       <c r="E35">
-        <v>7.893544733861833</v>
+        <v>-6.1316657623216173</v>
       </c>
       <c r="F35">
-        <v>-7.7241662534093747</v>
+        <v>-8.776541353383454</v>
       </c>
       <c r="G35">
-        <v>8.3598726114649615</v>
+        <v>-2.6578947368421058</v>
       </c>
       <c r="K35" t="s">
         <v>59</v>
@@ -94848,22 +91482,22 @@
         <v>59</v>
       </c>
       <c r="B36" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C36">
-        <v>-2.6315789473684315</v>
+        <v>3.2094594594594725</v>
       </c>
       <c r="D36">
-        <v>-2.4711696869851827</v>
+        <v>1.9790176442537086</v>
       </c>
       <c r="E36">
-        <v>0.58252427184464772</v>
+        <v>-0.5811250581125057</v>
       </c>
       <c r="F36">
-        <v>6.4474698176213669</v>
+        <v>11.004412146379449</v>
       </c>
       <c r="G36">
-        <v>51.020408163265294</v>
+        <v>48.972483455242084</v>
       </c>
       <c r="K36" t="s">
         <v>60</v>
@@ -94874,22 +91508,22 @@
         <v>60</v>
       </c>
       <c r="B37" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C37">
-        <v>5.9915820747709869</v>
+        <v>3.4220976407381363</v>
       </c>
       <c r="D37">
-        <v>4.3255757280370561</v>
+        <v>3.7492677211482168</v>
       </c>
       <c r="E37">
-        <v>20.303498665167911</v>
+        <v>12.702049128165974</v>
       </c>
       <c r="F37">
-        <v>11.22369446609509</v>
+        <v>15.104640582347576</v>
       </c>
       <c r="G37">
-        <v>11.108227355307555</v>
+        <v>9.2670286278380942</v>
       </c>
       <c r="K37" t="s">
         <v>61</v>
@@ -94900,22 +91534,22 @@
         <v>61</v>
       </c>
       <c r="B38" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C38">
-        <v>3.553541616980687</v>
+        <v>0.67941040994933599</v>
       </c>
       <c r="D38">
-        <v>3.7267080745341672</v>
+        <v>0.71420343278424669</v>
       </c>
       <c r="E38">
-        <v>12.991997918157569</v>
+        <v>6.2074829931972779</v>
       </c>
       <c r="F38">
-        <v>11.088842931155794</v>
+        <v>13.427607680332136</v>
       </c>
       <c r="G38">
-        <v>34.378707381234854</v>
+        <v>26.301343477632798</v>
       </c>
       <c r="K38" t="s">
         <v>62</v>
@@ -94926,22 +91560,22 @@
         <v>63</v>
       </c>
       <c r="B39" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C39">
-        <v>-0.96383044875116131</v>
+        <v>-4.8723315194642174</v>
       </c>
       <c r="D39">
-        <v>1.0767701127541267</v>
+        <v>-1.1504751962767275</v>
       </c>
       <c r="E39">
-        <v>2.1922789006523367</v>
+        <v>-7.6047405118614488</v>
       </c>
       <c r="F39">
-        <v>-9.7622240268938025</v>
+        <v>-10.067273446774831</v>
       </c>
       <c r="G39">
-        <v>-21.513872234177107</v>
+        <v>-29.253183077545692</v>
       </c>
       <c r="K39" t="s">
         <v>64</v>
@@ -94952,22 +91586,22 @@
         <v>64</v>
       </c>
       <c r="B40" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C40">
-        <v>4.4215772972103755</v>
+        <v>-1.0701362691508094</v>
       </c>
       <c r="D40">
-        <v>2.5663297536323326</v>
+        <v>0.26529338327091406</v>
       </c>
       <c r="E40">
-        <v>24.702380952380942</v>
+        <v>9.6697106767943986</v>
       </c>
       <c r="F40">
-        <v>14.875740691606964</v>
+        <v>13.275740479548661</v>
       </c>
       <c r="G40">
-        <v>19.329352319706011</v>
+        <v>9.9324150911113005</v>
       </c>
       <c r="K40" t="s">
         <v>65</v>
@@ -94978,22 +91612,22 @@
         <v>65</v>
       </c>
       <c r="B41" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C41">
-        <v>5.2175920581784725</v>
+        <v>0.69116840373011024</v>
       </c>
       <c r="D41">
-        <v>3.0642243328810581</v>
+        <v>1.2018965707354763</v>
       </c>
       <c r="E41">
-        <v>22.07044328378198</v>
+        <v>7.8749412317818557</v>
       </c>
       <c r="F41">
-        <v>9.5157995914934546</v>
+        <v>11.926829268292684</v>
       </c>
       <c r="G41">
-        <v>-8.566556324606271</v>
+        <v>-12.723468999619621</v>
       </c>
       <c r="K41" t="s">
         <v>16</v>
@@ -95004,22 +91638,22 @@
         <v>16</v>
       </c>
       <c r="B42" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C42">
-        <v>1.0377908345892992</v>
+        <v>-4.1959922355571022</v>
       </c>
       <c r="D42">
-        <v>3.5162066334127413</v>
+        <v>-4.1554720047264535</v>
       </c>
       <c r="E42">
-        <v>-1.4531973516348442</v>
+        <v>-6.6987772704113215</v>
       </c>
       <c r="F42">
-        <v>-7.4710112131773077</v>
+        <v>-9.1105946994384848</v>
       </c>
       <c r="G42">
-        <v>40.331943639727868</v>
+        <v>42.200056328830961</v>
       </c>
       <c r="K42" t="s">
         <v>66</v>
@@ -95030,22 +91664,22 @@
         <v>66</v>
       </c>
       <c r="B43" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C43">
-        <v>5.8511408671380272</v>
+        <v>-6.5240356665477828</v>
       </c>
       <c r="D43">
-        <v>10.02162250930588</v>
+        <v>-12.089838537896815</v>
       </c>
       <c r="E43">
-        <v>5.1189853556485243</v>
+        <v>-8.1767289095099009</v>
       </c>
       <c r="F43">
-        <v>-4.2004289799809404</v>
+        <v>-3.154718516097184</v>
       </c>
       <c r="G43">
-        <v>146.03684661525276</v>
+        <v>133.68991083363053</v>
       </c>
       <c r="K43" t="s">
         <v>67</v>
@@ -95056,22 +91690,22 @@
         <v>67</v>
       </c>
       <c r="B44" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C44">
-        <v>2.2267484055805413</v>
+        <v>-4.2927196419141298</v>
       </c>
       <c r="D44">
-        <v>4.8534260092722405</v>
+        <v>-7.3084689642071989</v>
       </c>
       <c r="E44">
-        <v>0.37089215616002591</v>
+        <v>-7.2299353064691694</v>
       </c>
       <c r="F44">
-        <v>-4.1478328204373787</v>
+        <v>-6.7206197920364241</v>
       </c>
       <c r="G44">
-        <v>105.34144879910895</v>
+        <v>99.040600324587189</v>
       </c>
       <c r="K44" t="s">
         <v>68</v>
@@ -95082,22 +91716,22 @@
         <v>68</v>
       </c>
       <c r="B45" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C45">
-        <v>-3.2080719229027816</v>
+        <v>-5.4644441457185078</v>
       </c>
       <c r="D45">
-        <v>1.0124873439082012</v>
+        <v>-7.3756997036549228</v>
       </c>
       <c r="E45">
-        <v>-2.83729385794053</v>
+        <v>-12.137681159420287</v>
       </c>
       <c r="F45">
-        <v>-14.092996555683124</v>
+        <v>-19.953332195094184</v>
       </c>
       <c r="G45">
-        <v>52.470708099847172</v>
+        <v>46.57148812005002</v>
       </c>
       <c r="K45" t="s">
         <v>14</v>
@@ -95108,22 +91742,22 @@
         <v>14</v>
       </c>
       <c r="B46" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C46">
-        <v>6.2036444830556778</v>
+        <v>4.0006401024163869E-2</v>
       </c>
       <c r="D46">
-        <v>8.7144122646223181</v>
+        <v>-2.5259218835269421</v>
       </c>
       <c r="E46">
-        <v>7.0336423842144589</v>
+        <v>2.2405756807588597</v>
       </c>
       <c r="F46">
-        <v>5.6072448367255685</v>
+        <v>7.7287609856970567</v>
       </c>
       <c r="G46">
-        <v>36.629802444911377</v>
+        <v>37.229722313686743</v>
       </c>
       <c r="K46" t="s">
         <v>15</v>
@@ -95134,22 +91768,22 @@
         <v>15</v>
       </c>
       <c r="B47" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C47">
-        <v>-2.893861228399516</v>
+        <v>13.016135336292836</v>
       </c>
       <c r="D47">
-        <v>-6.9817723512783969</v>
+        <v>9.9622681124611319</v>
       </c>
       <c r="E47">
-        <v>2.5059520179864743</v>
+        <v>28.610609824556509</v>
       </c>
       <c r="F47">
-        <v>53.164161943013369</v>
+        <v>65.424139189892045</v>
       </c>
       <c r="G47">
-        <v>62.225496335249964</v>
+        <v>72.571605597520588</v>
       </c>
       <c r="K47" t="s">
         <v>69</v>
@@ -95160,22 +91794,22 @@
         <v>69</v>
       </c>
       <c r="B48" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C48">
-        <v>-3.2633822782209152</v>
+        <v>9.9220025055687806</v>
       </c>
       <c r="D48">
-        <v>-8.5634398902058368</v>
+        <v>6.8419502330780464</v>
       </c>
       <c r="E48">
-        <v>9.9159657454290269</v>
+        <v>23.190967401959096</v>
       </c>
       <c r="F48">
-        <v>50.778097103239816</v>
+        <v>58.26580858264483</v>
       </c>
       <c r="G48">
-        <v>63.730244702939196</v>
+        <v>70.218615407262845</v>
       </c>
       <c r="K48" t="s">
         <v>70</v>
@@ -95186,22 +91820,22 @@
         <v>70</v>
       </c>
       <c r="B49" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C49">
-        <v>1.7625897908382351</v>
+        <v>10.083427124798272</v>
       </c>
       <c r="D49">
-        <v>-1.3254274089535145</v>
+        <v>4.2955355955562995</v>
       </c>
       <c r="E49">
-        <v>6.8353472879645993</v>
+        <v>13.500377181401966</v>
       </c>
       <c r="F49">
-        <v>-10.44634390043359</v>
+        <v>0.79708023350011148</v>
       </c>
       <c r="G49">
-        <v>-25.454545555064485</v>
+        <v>-8.9682037843224833</v>
       </c>
       <c r="K49" t="s">
         <v>71</v>
@@ -95212,22 +91846,22 @@
         <v>71</v>
       </c>
       <c r="B50" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C50">
-        <v>1.241636730559867</v>
+        <v>5.0498882960057676</v>
       </c>
       <c r="D50">
-        <v>-1.910047335391964</v>
+        <v>3.2102049727752964</v>
       </c>
       <c r="E50">
-        <v>6.2154389604108404</v>
+        <v>20.56278903130513</v>
       </c>
       <c r="F50">
-        <v>63.719060479217113</v>
+        <v>62.623583378312645</v>
       </c>
       <c r="G50">
-        <v>93.350752610085891</v>
+        <v>91.34822921375131</v>
       </c>
       <c r="K50" t="s">
         <v>72</v>
@@ -95238,22 +91872,22 @@
         <v>72</v>
       </c>
       <c r="B51" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C51">
-        <v>-7.5100929301009076E-2</v>
+        <v>5.5746159345443065</v>
       </c>
       <c r="D51">
-        <v>-3.8975985396776371</v>
+        <v>3.4307456015215858</v>
       </c>
       <c r="E51">
-        <v>18.279391939873253</v>
+        <v>23.911740553899559</v>
       </c>
       <c r="F51">
-        <v>81.540248187870546</v>
+        <v>89.192072162783234</v>
       </c>
       <c r="G51">
-        <v>70.389867738084348</v>
+        <v>73.839760022577934</v>
       </c>
       <c r="K51" t="s">
         <v>73</v>
@@ -95264,22 +91898,22 @@
         <v>73</v>
       </c>
       <c r="B52" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C52">
-        <v>-2.2975077881619934</v>
+        <v>-1.5942606616181692</v>
       </c>
       <c r="D52">
-        <v>-2.2213561964146544</v>
+        <v>-3.9299610894941557</v>
       </c>
       <c r="E52">
-        <v>-3.5000000000000004</v>
+        <v>-1.0024057738572574</v>
       </c>
       <c r="F52">
-        <v>-4.4190476190476193</v>
+        <v>-2.2565320665083144</v>
       </c>
       <c r="G52">
-        <v>49.957564818245928</v>
+        <v>41.759680308667512</v>
       </c>
       <c r="K52" t="s">
         <v>74</v>
@@ -95290,22 +91924,22 @@
         <v>74</v>
       </c>
       <c r="B53" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C53">
-        <v>-4.0728476821192094</v>
+        <v>-1.760441836382453</v>
       </c>
       <c r="D53">
-        <v>-4.1363335539377895</v>
+        <v>-4.6885465505693231</v>
       </c>
       <c r="E53">
-        <v>-3.465511496167955</v>
+        <v>-1.6246111303145485</v>
       </c>
       <c r="F53">
-        <v>-1.7299864314789766</v>
+        <v>-1.025908537645623</v>
       </c>
       <c r="G53">
-        <v>-27.055268790129674</v>
+        <v>-24.35880398671096</v>
       </c>
       <c r="K53" t="s">
         <v>75</v>
@@ -95316,22 +91950,22 @@
         <v>75</v>
       </c>
       <c r="B54" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C54">
-        <v>-1.7391304347826073</v>
+        <v>0.7488087134104916</v>
       </c>
       <c r="D54">
-        <v>-3.9241334205362959</v>
+        <v>-0.73775989268946629</v>
       </c>
       <c r="E54">
-        <v>6.8363636363636324</v>
+        <v>11.194590533433511</v>
       </c>
       <c r="F54">
-        <v>6.1416184971098247</v>
+        <v>4.4460127028934426</v>
       </c>
       <c r="G54">
-        <v>-17.379077615298097</v>
+        <v>-15.525114155251135</v>
       </c>
       <c r="K54" t="s">
         <v>76</v>
@@ -95342,22 +91976,22 @@
         <v>76</v>
       </c>
       <c r="B55" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C55">
-        <v>16.813405282590175</v>
+        <v>-2.6987600291757841</v>
       </c>
       <c r="D55">
-        <v>7.8961175236096537</v>
+        <v>-13.601036269430052</v>
       </c>
       <c r="E55">
-        <v>26.709796672828094</v>
+        <v>25.612052730696799</v>
       </c>
       <c r="F55">
-        <v>9.330143540669857</v>
+        <v>24.054556726596406</v>
       </c>
       <c r="G55">
-        <v>-56.184084372003838</v>
+        <v>-63.277665626720506</v>
       </c>
       <c r="K55" t="s">
         <v>77</v>
@@ -95368,22 +92002,22 @@
         <v>77</v>
       </c>
       <c r="B56" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C56">
-        <v>3.237629810629207</v>
+        <v>-4.0009484977096408</v>
       </c>
       <c r="D56">
-        <v>4.8647307024075479</v>
+        <v>-7.3259697642809289</v>
       </c>
       <c r="E56">
-        <v>15.405626877902215</v>
+        <v>5.0904345450783195</v>
       </c>
       <c r="F56">
-        <v>36.312308436844646</v>
+        <v>32.152715414931968</v>
       </c>
       <c r="G56">
-        <v>26.857829154781566</v>
+        <v>25.350587668193285</v>
       </c>
       <c r="K56" t="s">
         <v>78</v>
@@ -95394,22 +92028,22 @@
         <v>78</v>
       </c>
       <c r="B57" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C57">
-        <v>0.29679245914376501</v>
+        <v>-5.5540485850514072</v>
       </c>
       <c r="D57">
-        <v>2.0521785986031706</v>
+        <v>-4.4362088577404233</v>
       </c>
       <c r="E57">
-        <v>-3.6971174329996894</v>
+        <v>-10.327303277164528</v>
       </c>
       <c r="F57">
-        <v>-16.238802198189397</v>
+        <v>-19.315264050123421</v>
       </c>
       <c r="G57">
-        <v>-4.4240953833356329</v>
+        <v>-13.498073601700542</v>
       </c>
       <c r="K57" t="s">
         <v>79</v>
@@ -95420,22 +92054,22 @@
         <v>79</v>
       </c>
       <c r="B58" s="1">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="C58">
-        <v>-2.1007271747912766</v>
+        <v>8.6657496561210454</v>
       </c>
       <c r="D58">
-        <v>-0.81855388813096863</v>
+        <v>8.6657496561210454</v>
       </c>
       <c r="E58">
-        <v>0.16533480297603273</v>
+        <v>5.7280513918629481</v>
       </c>
       <c r="F58">
-        <v>4.5742232451093141</v>
+        <v>6.6990815775256642</v>
       </c>
       <c r="G58">
-        <v>0.55325034578146615</v>
+        <v>-1.5698978320458536</v>
       </c>
     </row>
   </sheetData>
